--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781414</v>
+        <v>119781352</v>
       </c>
       <c r="B67" t="n">
-        <v>86288</v>
+        <v>101074</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,25 +8068,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>426</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670832</v>
+        <v>670782</v>
       </c>
       <c r="R67" t="n">
-        <v>6983235</v>
+        <v>6983174</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781352</v>
+        <v>119781414</v>
       </c>
       <c r="B68" t="n">
-        <v>101074</v>
+        <v>86288</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8170,25 +8170,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>426</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670782</v>
+        <v>670832</v>
       </c>
       <c r="R68" t="n">
-        <v>6983174</v>
+        <v>6983235</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -10027,10 +10027,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788716</v>
+        <v>119788516</v>
       </c>
       <c r="B85" t="n">
-        <v>91494</v>
+        <v>57326</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10039,38 +10039,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>670864</v>
+        <v>670807</v>
       </c>
       <c r="R85" t="n">
-        <v>6983129</v>
+        <v>6983126</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10102,7 +10107,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10112,7 +10117,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10144,10 +10149,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788516</v>
+        <v>119788716</v>
       </c>
       <c r="B86" t="n">
-        <v>57326</v>
+        <v>91494</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10156,43 +10161,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670807</v>
+        <v>670864</v>
       </c>
       <c r="R86" t="n">
-        <v>6983126</v>
+        <v>6983129</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11864,10 +11864,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119899557</v>
+        <v>119895581</v>
       </c>
       <c r="B101" t="n">
-        <v>91494</v>
+        <v>91861</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11880,21 +11880,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119895581</v>
+        <v>119898984</v>
       </c>
       <c r="B102" t="n">
-        <v>91861</v>
+        <v>94311</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11992,34 +11992,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>2809</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670765</v>
+        <v>670792</v>
       </c>
       <c r="R102" t="n">
-        <v>6983124</v>
+        <v>6983157</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119898984</v>
+        <v>119899557</v>
       </c>
       <c r="B103" t="n">
-        <v>94311</v>
+        <v>91494</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12104,34 +12104,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670792</v>
+        <v>670765</v>
       </c>
       <c r="R103" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781352</v>
+        <v>119781414</v>
       </c>
       <c r="B67" t="n">
-        <v>101074</v>
+        <v>86288</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,25 +8068,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>426</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670782</v>
+        <v>670832</v>
       </c>
       <c r="R67" t="n">
-        <v>6983174</v>
+        <v>6983235</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781414</v>
+        <v>119781352</v>
       </c>
       <c r="B68" t="n">
-        <v>86288</v>
+        <v>101074</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8170,25 +8170,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>426</v>
+        <v>221235</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670832</v>
+        <v>670782</v>
       </c>
       <c r="R68" t="n">
-        <v>6983235</v>
+        <v>6983174</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -6525,10 +6525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119781440</v>
+        <v>119781414</v>
       </c>
       <c r="B52" t="n">
-        <v>91861</v>
+        <v>86288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,25 +6537,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>670899</v>
+        <v>670832</v>
       </c>
       <c r="R52" t="n">
-        <v>6983187</v>
+        <v>6983235</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781370</v>
+        <v>119781385</v>
       </c>
       <c r="B53" t="n">
-        <v>91494</v>
+        <v>89239</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6643,21 +6643,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4769</v>
+        <v>6268</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670776</v>
+        <v>670900</v>
       </c>
       <c r="R53" t="n">
-        <v>6983129</v>
+        <v>6983212</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781439</v>
+        <v>119781369</v>
       </c>
       <c r="B55" t="n">
-        <v>91861</v>
+        <v>91494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6847,21 +6847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670893</v>
+        <v>670819</v>
       </c>
       <c r="R55" t="n">
-        <v>6983206</v>
+        <v>6983261</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119781368</v>
+        <v>119781440</v>
       </c>
       <c r="B56" t="n">
-        <v>91494</v>
+        <v>91861</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>670847</v>
+        <v>670899</v>
       </c>
       <c r="R56" t="n">
-        <v>6983303</v>
+        <v>6983187</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781348</v>
+        <v>119781392</v>
       </c>
       <c r="B57" t="n">
-        <v>101074</v>
+        <v>91850</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7047,25 +7047,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221235</v>
+        <v>789</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670779</v>
+        <v>670901</v>
       </c>
       <c r="R57" t="n">
-        <v>6983126</v>
+        <v>6983185</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7137,7 +7137,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781448</v>
+        <v>119781449</v>
       </c>
       <c r="B58" t="n">
         <v>91858</v>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670902</v>
+        <v>670901</v>
       </c>
       <c r="R58" t="n">
-        <v>6983235</v>
+        <v>6983219</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119781361</v>
+        <v>119781352</v>
       </c>
       <c r="B59" t="n">
-        <v>104996</v>
+        <v>101074</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7255,21 +7255,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>224098</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>670789</v>
+        <v>670782</v>
       </c>
       <c r="R59" t="n">
-        <v>6983134</v>
+        <v>6983174</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7323,7 +7323,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7342,10 +7341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119781359</v>
+        <v>119781370</v>
       </c>
       <c r="B60" t="n">
-        <v>100080</v>
+        <v>91494</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7358,21 +7357,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7382,10 +7381,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670836</v>
+        <v>670776</v>
       </c>
       <c r="R60" t="n">
-        <v>6983189</v>
+        <v>6983129</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7444,10 +7443,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119781469</v>
+        <v>119781368</v>
       </c>
       <c r="B61" t="n">
-        <v>100171</v>
+        <v>91494</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7460,21 +7459,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7484,10 +7483,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670788</v>
+        <v>670847</v>
       </c>
       <c r="R61" t="n">
-        <v>6983134</v>
+        <v>6983303</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,10 +7545,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119781385</v>
+        <v>119781353</v>
       </c>
       <c r="B62" t="n">
-        <v>89239</v>
+        <v>101074</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7562,21 +7561,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6268</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7586,10 +7585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>670900</v>
+        <v>670761</v>
       </c>
       <c r="R62" t="n">
-        <v>6983212</v>
+        <v>6983130</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7648,10 +7647,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119781392</v>
+        <v>119781448</v>
       </c>
       <c r="B63" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7660,25 +7659,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>789</v>
+        <v>4368</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7688,10 +7687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>670901</v>
+        <v>670902</v>
       </c>
       <c r="R63" t="n">
-        <v>6983185</v>
+        <v>6983235</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7750,10 +7749,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119781470</v>
+        <v>119781350</v>
       </c>
       <c r="B64" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7766,21 +7765,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7790,10 +7789,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>670778</v>
+        <v>670791</v>
       </c>
       <c r="R64" t="n">
-        <v>6983109</v>
+        <v>6983132</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7852,10 +7851,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781369</v>
+        <v>119781361</v>
       </c>
       <c r="B65" t="n">
-        <v>91494</v>
+        <v>104996</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7868,21 +7867,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4769</v>
+        <v>224098</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7892,10 +7891,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670819</v>
+        <v>670789</v>
       </c>
       <c r="R65" t="n">
-        <v>6983261</v>
+        <v>6983134</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7936,6 +7935,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781447</v>
+        <v>119781348</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>101074</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,25 +7966,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670905</v>
+        <v>670779</v>
       </c>
       <c r="R66" t="n">
-        <v>6983220</v>
+        <v>6983126</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781414</v>
+        <v>119781438</v>
       </c>
       <c r="B67" t="n">
-        <v>86288</v>
+        <v>91861</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,25 +8068,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>426</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670832</v>
+        <v>670906</v>
       </c>
       <c r="R67" t="n">
-        <v>6983235</v>
+        <v>6983256</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781352</v>
+        <v>119781447</v>
       </c>
       <c r="B68" t="n">
-        <v>101074</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8170,25 +8170,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670782</v>
+        <v>670905</v>
       </c>
       <c r="R68" t="n">
-        <v>6983174</v>
+        <v>6983220</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781449</v>
+        <v>119781377</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>57326</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670901</v>
+        <v>670794</v>
       </c>
       <c r="R69" t="n">
-        <v>6983219</v>
+        <v>6983144</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8362,10 +8362,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119781353</v>
+        <v>119781470</v>
       </c>
       <c r="B70" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8378,21 +8378,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>670761</v>
+        <v>670778</v>
       </c>
       <c r="R70" t="n">
-        <v>6983130</v>
+        <v>6983109</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119781438</v>
+        <v>119781469</v>
       </c>
       <c r="B71" t="n">
-        <v>91861</v>
+        <v>100171</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8480,21 +8480,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>670906</v>
+        <v>670788</v>
       </c>
       <c r="R71" t="n">
-        <v>6983256</v>
+        <v>6983134</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119781377</v>
+        <v>119781439</v>
       </c>
       <c r="B72" t="n">
-        <v>57326</v>
+        <v>91861</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8578,25 +8578,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>670794</v>
+        <v>670893</v>
       </c>
       <c r="R72" t="n">
-        <v>6983144</v>
+        <v>6983206</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119781350</v>
+        <v>119781359</v>
       </c>
       <c r="B73" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8684,21 +8684,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>670791</v>
+        <v>670836</v>
       </c>
       <c r="R73" t="n">
-        <v>6983132</v>
+        <v>6983189</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119789841</v>
+        <v>119789443</v>
       </c>
       <c r="B74" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8786,21 +8786,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>670817</v>
+        <v>670906</v>
       </c>
       <c r="R74" t="n">
-        <v>6983220</v>
+        <v>6983132</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8882,7 +8882,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119788502</v>
+        <v>119789861</v>
       </c>
       <c r="B75" t="n">
         <v>100171</v>
@@ -8918,14 +8918,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>670807</v>
+        <v>670873</v>
       </c>
       <c r="R75" t="n">
-        <v>6983126</v>
+        <v>6983173</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8994,7 +8994,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119789062</v>
+        <v>119804619</v>
       </c>
       <c r="B76" t="n">
         <v>100171</v>
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>670848</v>
+        <v>670802</v>
       </c>
       <c r="R76" t="n">
-        <v>6983160</v>
+        <v>6983219</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9090,11 +9090,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9111,10 +9106,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788496</v>
+        <v>119789925</v>
       </c>
       <c r="B77" t="n">
-        <v>101074</v>
+        <v>94311</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9127,34 +9122,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>670807</v>
+        <v>670884</v>
       </c>
       <c r="R77" t="n">
-        <v>6983126</v>
+        <v>6983286</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9186,7 +9181,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9196,7 +9191,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9207,11 +9202,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9228,10 +9218,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788949</v>
+        <v>119804612</v>
       </c>
       <c r="B78" t="n">
-        <v>100171</v>
+        <v>94311</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9244,21 +9234,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9268,10 +9258,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670878</v>
+        <v>670802</v>
       </c>
       <c r="R78" t="n">
-        <v>6983130</v>
+        <v>6983219</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9303,7 +9293,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9313,7 +9303,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9340,7 +9330,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119789443</v>
+        <v>119788949</v>
       </c>
       <c r="B79" t="n">
         <v>100171</v>
@@ -9380,10 +9370,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670906</v>
+        <v>670878</v>
       </c>
       <c r="R79" t="n">
-        <v>6983132</v>
+        <v>6983130</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9415,7 +9405,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9425,7 +9415,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9452,10 +9442,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119789925</v>
+        <v>119788516</v>
       </c>
       <c r="B80" t="n">
-        <v>94311</v>
+        <v>57326</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9464,38 +9454,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>670884</v>
+        <v>670807</v>
       </c>
       <c r="R80" t="n">
-        <v>6983286</v>
+        <v>6983126</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9527,7 +9522,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9537,7 +9532,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9548,6 +9543,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9564,10 +9564,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789399</v>
+        <v>119788496</v>
       </c>
       <c r="B81" t="n">
-        <v>91494</v>
+        <v>101074</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9580,34 +9580,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670892</v>
+        <v>670807</v>
       </c>
       <c r="R81" t="n">
-        <v>6983131</v>
+        <v>6983126</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9660,6 +9660,11 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9676,7 +9681,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119789352</v>
+        <v>119789062</v>
       </c>
       <c r="B82" t="n">
         <v>100171</v>
@@ -9716,10 +9721,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670892</v>
+        <v>670848</v>
       </c>
       <c r="R82" t="n">
-        <v>6983131</v>
+        <v>6983160</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9751,7 +9756,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9761,7 +9766,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9793,10 +9798,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788402</v>
+        <v>119788716</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>91494</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9805,38 +9810,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>670846</v>
+        <v>670864</v>
       </c>
       <c r="R83" t="n">
-        <v>6983191</v>
+        <v>6983129</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9868,7 +9873,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9878,12 +9883,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119804612</v>
+        <v>119788502</v>
       </c>
       <c r="B84" t="n">
-        <v>94311</v>
+        <v>100171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9931,34 +9931,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670802</v>
+        <v>670807</v>
       </c>
       <c r="R84" t="n">
-        <v>6983219</v>
+        <v>6983126</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10027,10 +10027,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788516</v>
+        <v>119789399</v>
       </c>
       <c r="B85" t="n">
-        <v>57326</v>
+        <v>91494</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10039,43 +10039,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>670807</v>
+        <v>670892</v>
       </c>
       <c r="R85" t="n">
-        <v>6983126</v>
+        <v>6983131</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10107,7 +10102,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10117,7 +10112,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10128,11 +10123,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10149,10 +10139,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788716</v>
+        <v>119789352</v>
       </c>
       <c r="B86" t="n">
-        <v>91494</v>
+        <v>100171</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10165,34 +10155,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670864</v>
+        <v>670892</v>
       </c>
       <c r="R86" t="n">
-        <v>6983129</v>
+        <v>6983131</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10224,7 +10214,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10234,7 +10224,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10266,10 +10256,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119789381</v>
+        <v>119788402</v>
       </c>
       <c r="B87" t="n">
-        <v>100080</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10278,25 +10268,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>4368</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10306,10 +10296,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>670878</v>
+        <v>670846</v>
       </c>
       <c r="R87" t="n">
-        <v>6983130</v>
+        <v>6983191</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10341,7 +10331,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10351,7 +10341,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10362,6 +10357,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10495,10 +10495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119789861</v>
+        <v>119789841</v>
       </c>
       <c r="B89" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10511,21 +10511,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>670873</v>
+        <v>670817</v>
       </c>
       <c r="R89" t="n">
-        <v>6983173</v>
+        <v>6983220</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10607,10 +10607,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119804619</v>
+        <v>119789381</v>
       </c>
       <c r="B90" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10623,21 +10623,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>670802</v>
+        <v>670878</v>
       </c>
       <c r="R90" t="n">
-        <v>6983219</v>
+        <v>6983130</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119898844</v>
+        <v>119899641</v>
       </c>
       <c r="B92" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10857,34 +10857,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670832</v>
+        <v>670779</v>
       </c>
       <c r="R92" t="n">
-        <v>6983190</v>
+        <v>6983125</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119899526</v>
+        <v>119898932</v>
       </c>
       <c r="B93" t="n">
-        <v>104994</v>
+        <v>94323</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,34 +10969,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>2813</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670765</v>
+        <v>670806</v>
       </c>
       <c r="R93" t="n">
-        <v>6983124</v>
+        <v>6983157</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11065,10 +11065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898932</v>
+        <v>119898558</v>
       </c>
       <c r="B94" t="n">
-        <v>94323</v>
+        <v>100171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11081,21 +11081,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670806</v>
+        <v>670818</v>
       </c>
       <c r="R94" t="n">
-        <v>6983157</v>
+        <v>6983189</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11177,10 +11177,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898809</v>
+        <v>119899557</v>
       </c>
       <c r="B95" t="n">
-        <v>100171</v>
+        <v>91494</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11193,34 +11193,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670818</v>
+        <v>670765</v>
       </c>
       <c r="R95" t="n">
-        <v>6983189</v>
+        <v>6983124</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11289,10 +11289,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119899251</v>
+        <v>119898937</v>
       </c>
       <c r="B96" t="n">
-        <v>100080</v>
+        <v>94311</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11305,39 +11305,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670777</v>
+        <v>670806</v>
       </c>
       <c r="R96" t="n">
-        <v>6983156</v>
+        <v>6983157</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11369,7 +11364,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11379,7 +11374,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11390,11 +11385,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11411,10 +11401,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898656</v>
+        <v>119898984</v>
       </c>
       <c r="B97" t="n">
-        <v>101074</v>
+        <v>94311</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11427,21 +11417,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11451,10 +11441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670818</v>
+        <v>670792</v>
       </c>
       <c r="R97" t="n">
-        <v>6983189</v>
+        <v>6983157</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11486,7 +11476,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11496,7 +11486,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11507,11 +11497,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11528,7 +11513,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119900032</v>
+        <v>119895594</v>
       </c>
       <c r="B98" t="n">
         <v>100080</v>
@@ -11564,14 +11549,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670742</v>
+        <v>670802</v>
       </c>
       <c r="R98" t="n">
-        <v>6983030</v>
+        <v>6983219</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11603,7 +11588,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11613,7 +11598,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11640,10 +11625,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119895594</v>
+        <v>119898758</v>
       </c>
       <c r="B99" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11656,21 +11641,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11680,10 +11665,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670802</v>
+        <v>670804</v>
       </c>
       <c r="R99" t="n">
-        <v>6983219</v>
+        <v>6983188</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11715,7 +11700,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11725,7 +11710,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11736,6 +11721,11 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11752,10 +11742,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898741</v>
+        <v>119898913</v>
       </c>
       <c r="B100" t="n">
-        <v>100080</v>
+        <v>57326</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11764,25 +11754,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11792,10 +11782,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670804</v>
+        <v>670820</v>
       </c>
       <c r="R100" t="n">
-        <v>6983188</v>
+        <v>6983158</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11827,7 +11817,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11837,7 +11827,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11864,10 +11854,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119895581</v>
+        <v>119898495</v>
       </c>
       <c r="B101" t="n">
-        <v>91861</v>
+        <v>57326</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11876,41 +11866,51 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670765</v>
+        <v>670817</v>
       </c>
       <c r="R101" t="n">
-        <v>6983124</v>
+        <v>6983220</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898984</v>
+        <v>119898741</v>
       </c>
       <c r="B102" t="n">
-        <v>94311</v>
+        <v>100080</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11992,21 +11992,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2809</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670792</v>
+        <v>670804</v>
       </c>
       <c r="R102" t="n">
-        <v>6983157</v>
+        <v>6983188</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119899557</v>
+        <v>119895581</v>
       </c>
       <c r="B103" t="n">
-        <v>91494</v>
+        <v>91861</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12104,21 +12104,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12200,10 +12200,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898506</v>
+        <v>119898844</v>
       </c>
       <c r="B104" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12216,21 +12216,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12240,10 +12240,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670802</v>
+        <v>670832</v>
       </c>
       <c r="R104" t="n">
-        <v>6983219</v>
+        <v>6983190</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12296,11 +12296,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12317,7 +12312,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119898663</v>
+        <v>119899251</v>
       </c>
       <c r="B105" t="n">
         <v>100080</v>
@@ -12351,16 +12346,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670818</v>
+        <v>670777</v>
       </c>
       <c r="R105" t="n">
-        <v>6983189</v>
+        <v>6983156</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12434,10 +12434,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898495</v>
+        <v>119898663</v>
       </c>
       <c r="B106" t="n">
-        <v>57326</v>
+        <v>100080</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12446,51 +12446,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670817</v>
+        <v>670818</v>
       </c>
       <c r="R106" t="n">
-        <v>6983220</v>
+        <v>6983189</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12519,7 +12509,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12529,7 +12519,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12540,6 +12530,11 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12556,10 +12551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119898758</v>
+        <v>119898656</v>
       </c>
       <c r="B107" t="n">
-        <v>91861</v>
+        <v>101074</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12572,21 +12567,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12596,10 +12591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670804</v>
+        <v>670818</v>
       </c>
       <c r="R107" t="n">
-        <v>6983188</v>
+        <v>6983189</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12631,7 +12626,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12641,7 +12636,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12673,10 +12668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119898937</v>
+        <v>119900032</v>
       </c>
       <c r="B108" t="n">
-        <v>94311</v>
+        <v>100080</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12689,34 +12684,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2809</v>
+        <v>222771</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670806</v>
+        <v>670742</v>
       </c>
       <c r="R108" t="n">
-        <v>6983157</v>
+        <v>6983030</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12748,7 +12743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12758,7 +12753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12785,10 +12780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119898913</v>
+        <v>119898506</v>
       </c>
       <c r="B109" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12797,25 +12792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12825,10 +12820,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670820</v>
+        <v>670802</v>
       </c>
       <c r="R109" t="n">
-        <v>6983158</v>
+        <v>6983219</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12860,7 +12855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12870,7 +12865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12881,6 +12876,11 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12897,10 +12897,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119899641</v>
+        <v>119899526</v>
       </c>
       <c r="B110" t="n">
-        <v>101074</v>
+        <v>104994</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12913,21 +12913,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221235</v>
+        <v>221725</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670779</v>
+        <v>670765</v>
       </c>
       <c r="R110" t="n">
-        <v>6983125</v>
+        <v>6983124</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -6627,10 +6627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781385</v>
+        <v>119781410</v>
       </c>
       <c r="B53" t="n">
-        <v>89239</v>
+        <v>91848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6639,25 +6639,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6268</v>
+        <v>2058</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670900</v>
+        <v>670897</v>
       </c>
       <c r="R53" t="n">
-        <v>6983212</v>
+        <v>6983186</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119781410</v>
+        <v>119781369</v>
       </c>
       <c r="B54" t="n">
-        <v>91848</v>
+        <v>91494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6741,25 +6741,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2058</v>
+        <v>4769</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>670897</v>
+        <v>670819</v>
       </c>
       <c r="R54" t="n">
-        <v>6983186</v>
+        <v>6983261</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781369</v>
+        <v>119781385</v>
       </c>
       <c r="B55" t="n">
-        <v>91494</v>
+        <v>89239</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6847,21 +6847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4769</v>
+        <v>6268</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670819</v>
+        <v>670900</v>
       </c>
       <c r="R55" t="n">
-        <v>6983261</v>
+        <v>6983212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781348</v>
+        <v>119781438</v>
       </c>
       <c r="B66" t="n">
-        <v>101074</v>
+        <v>91861</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7970,21 +7970,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670779</v>
+        <v>670906</v>
       </c>
       <c r="R66" t="n">
-        <v>6983126</v>
+        <v>6983256</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781438</v>
+        <v>119781348</v>
       </c>
       <c r="B67" t="n">
-        <v>91861</v>
+        <v>101074</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8072,21 +8072,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670906</v>
+        <v>670779</v>
       </c>
       <c r="R67" t="n">
-        <v>6983256</v>
+        <v>6983126</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781447</v>
+        <v>119781377</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>57326</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670905</v>
+        <v>670794</v>
       </c>
       <c r="R68" t="n">
-        <v>6983220</v>
+        <v>6983144</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781377</v>
+        <v>119781447</v>
       </c>
       <c r="B69" t="n">
-        <v>57326</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>4368</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670794</v>
+        <v>670905</v>
       </c>
       <c r="R69" t="n">
-        <v>6983144</v>
+        <v>6983220</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -12551,10 +12551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119898656</v>
+        <v>119900032</v>
       </c>
       <c r="B107" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12567,34 +12567,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670818</v>
+        <v>670742</v>
       </c>
       <c r="R107" t="n">
-        <v>6983189</v>
+        <v>6983030</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12647,11 +12647,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12668,10 +12663,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119900032</v>
+        <v>119898656</v>
       </c>
       <c r="B108" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12684,34 +12679,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670742</v>
+        <v>670818</v>
       </c>
       <c r="R108" t="n">
-        <v>6983030</v>
+        <v>6983189</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12743,7 +12738,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12753,7 +12748,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12764,6 +12759,11 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -6525,10 +6525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119781414</v>
+        <v>119781352</v>
       </c>
       <c r="B52" t="n">
-        <v>86288</v>
+        <v>101074</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,25 +6537,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>426</v>
+        <v>221235</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>670832</v>
+        <v>670782</v>
       </c>
       <c r="R52" t="n">
-        <v>6983235</v>
+        <v>6983174</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781410</v>
+        <v>119781368</v>
       </c>
       <c r="B53" t="n">
-        <v>91848</v>
+        <v>91494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6639,25 +6639,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2058</v>
+        <v>4769</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670897</v>
+        <v>670847</v>
       </c>
       <c r="R53" t="n">
-        <v>6983186</v>
+        <v>6983303</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119781369</v>
+        <v>119781439</v>
       </c>
       <c r="B54" t="n">
-        <v>91494</v>
+        <v>91861</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>670819</v>
+        <v>670893</v>
       </c>
       <c r="R54" t="n">
-        <v>6983261</v>
+        <v>6983206</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781385</v>
+        <v>119781414</v>
       </c>
       <c r="B55" t="n">
-        <v>89239</v>
+        <v>86288</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6843,25 +6843,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6268</v>
+        <v>426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670900</v>
+        <v>670832</v>
       </c>
       <c r="R55" t="n">
-        <v>6983212</v>
+        <v>6983235</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119781440</v>
+        <v>119781385</v>
       </c>
       <c r="B56" t="n">
-        <v>91861</v>
+        <v>89239</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>6268</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>670899</v>
+        <v>670900</v>
       </c>
       <c r="R56" t="n">
-        <v>6983187</v>
+        <v>6983212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781392</v>
+        <v>119781361</v>
       </c>
       <c r="B57" t="n">
-        <v>91850</v>
+        <v>104996</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7047,25 +7047,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>789</v>
+        <v>224098</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670901</v>
+        <v>670789</v>
       </c>
       <c r="R57" t="n">
-        <v>6983185</v>
+        <v>6983134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7119,6 +7119,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7137,10 +7138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781449</v>
+        <v>119781410</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>91848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7149,25 +7150,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>2058</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7177,10 +7178,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670901</v>
+        <v>670897</v>
       </c>
       <c r="R58" t="n">
-        <v>6983219</v>
+        <v>6983186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7239,7 +7240,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119781352</v>
+        <v>119781353</v>
       </c>
       <c r="B59" t="n">
         <v>101074</v>
@@ -7279,10 +7280,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>670782</v>
+        <v>670761</v>
       </c>
       <c r="R59" t="n">
-        <v>6983174</v>
+        <v>6983130</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7341,10 +7342,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119781370</v>
+        <v>119781469</v>
       </c>
       <c r="B60" t="n">
-        <v>91494</v>
+        <v>100171</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7357,21 +7358,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7381,10 +7382,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670776</v>
+        <v>670788</v>
       </c>
       <c r="R60" t="n">
-        <v>6983129</v>
+        <v>6983134</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7443,10 +7444,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119781368</v>
+        <v>119781438</v>
       </c>
       <c r="B61" t="n">
-        <v>91494</v>
+        <v>91861</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7459,21 +7460,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7483,10 +7484,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670847</v>
+        <v>670906</v>
       </c>
       <c r="R61" t="n">
-        <v>6983303</v>
+        <v>6983256</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,10 +7546,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119781353</v>
+        <v>119781448</v>
       </c>
       <c r="B62" t="n">
-        <v>101074</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7557,25 +7558,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7585,10 +7586,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>670761</v>
+        <v>670902</v>
       </c>
       <c r="R62" t="n">
-        <v>6983130</v>
+        <v>6983235</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7647,10 +7648,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119781448</v>
+        <v>119781440</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7659,25 +7660,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7687,10 +7688,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>670902</v>
+        <v>670899</v>
       </c>
       <c r="R63" t="n">
-        <v>6983235</v>
+        <v>6983187</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7749,10 +7750,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119781350</v>
+        <v>119781377</v>
       </c>
       <c r="B64" t="n">
-        <v>101074</v>
+        <v>57326</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7761,25 +7762,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7789,10 +7790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>670791</v>
+        <v>670794</v>
       </c>
       <c r="R64" t="n">
-        <v>6983132</v>
+        <v>6983144</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7851,10 +7852,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781361</v>
+        <v>119781392</v>
       </c>
       <c r="B65" t="n">
-        <v>104996</v>
+        <v>91850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7863,25 +7864,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>224098</v>
+        <v>789</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7891,10 +7892,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670789</v>
+        <v>670901</v>
       </c>
       <c r="R65" t="n">
-        <v>6983134</v>
+        <v>6983185</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7935,7 +7936,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781438</v>
+        <v>119781369</v>
       </c>
       <c r="B66" t="n">
-        <v>91861</v>
+        <v>91494</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7970,21 +7970,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670906</v>
+        <v>670819</v>
       </c>
       <c r="R66" t="n">
-        <v>6983256</v>
+        <v>6983261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781348</v>
+        <v>119781449</v>
       </c>
       <c r="B67" t="n">
-        <v>101074</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,25 +8068,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670779</v>
+        <v>670901</v>
       </c>
       <c r="R67" t="n">
-        <v>6983126</v>
+        <v>6983219</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781377</v>
+        <v>119781350</v>
       </c>
       <c r="B68" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8170,25 +8170,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670794</v>
+        <v>670791</v>
       </c>
       <c r="R68" t="n">
-        <v>6983144</v>
+        <v>6983132</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781447</v>
+        <v>119781470</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>100171</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8272,25 +8272,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670905</v>
+        <v>670778</v>
       </c>
       <c r="R69" t="n">
-        <v>6983220</v>
+        <v>6983109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8362,10 +8362,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119781470</v>
+        <v>119781348</v>
       </c>
       <c r="B70" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8378,21 +8378,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>670778</v>
+        <v>670779</v>
       </c>
       <c r="R70" t="n">
-        <v>6983109</v>
+        <v>6983126</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119781469</v>
+        <v>119781359</v>
       </c>
       <c r="B71" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8480,21 +8480,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>670788</v>
+        <v>670836</v>
       </c>
       <c r="R71" t="n">
-        <v>6983134</v>
+        <v>6983189</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119781439</v>
+        <v>119781370</v>
       </c>
       <c r="B72" t="n">
-        <v>91861</v>
+        <v>91494</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8582,21 +8582,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>670893</v>
+        <v>670776</v>
       </c>
       <c r="R72" t="n">
-        <v>6983206</v>
+        <v>6983129</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119781359</v>
+        <v>119781447</v>
       </c>
       <c r="B73" t="n">
-        <v>100080</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8680,25 +8680,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222771</v>
+        <v>4368</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>670836</v>
+        <v>670905</v>
       </c>
       <c r="R73" t="n">
-        <v>6983189</v>
+        <v>6983220</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119789443</v>
+        <v>119788402</v>
       </c>
       <c r="B74" t="n">
-        <v>100171</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8782,25 +8782,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>670906</v>
+        <v>670846</v>
       </c>
       <c r="R74" t="n">
-        <v>6983132</v>
+        <v>6983191</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8855,7 +8855,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8866,6 +8871,11 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8994,10 +9004,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119804619</v>
+        <v>119789841</v>
       </c>
       <c r="B76" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9010,21 +9020,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9034,10 +9044,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>670802</v>
+        <v>670817</v>
       </c>
       <c r="R76" t="n">
-        <v>6983219</v>
+        <v>6983220</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9069,7 +9079,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9079,7 +9089,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9106,10 +9116,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119789925</v>
+        <v>119789062</v>
       </c>
       <c r="B77" t="n">
-        <v>94311</v>
+        <v>100171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9122,34 +9132,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>670884</v>
+        <v>670848</v>
       </c>
       <c r="R77" t="n">
-        <v>6983286</v>
+        <v>6983160</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9181,7 +9191,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9191,7 +9201,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9202,6 +9212,11 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9218,10 +9233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119804612</v>
+        <v>119788949</v>
       </c>
       <c r="B78" t="n">
-        <v>94311</v>
+        <v>100171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9234,21 +9249,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9258,10 +9273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670802</v>
+        <v>670878</v>
       </c>
       <c r="R78" t="n">
-        <v>6983219</v>
+        <v>6983130</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9293,7 +9308,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9303,7 +9318,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9330,7 +9345,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788949</v>
+        <v>119789631</v>
       </c>
       <c r="B79" t="n">
         <v>100171</v>
@@ -9370,10 +9385,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670878</v>
+        <v>670906</v>
       </c>
       <c r="R79" t="n">
-        <v>6983130</v>
+        <v>6983132</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9405,7 +9420,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9415,7 +9430,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9442,10 +9457,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788516</v>
+        <v>119804619</v>
       </c>
       <c r="B80" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9454,43 +9469,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>670807</v>
+        <v>670802</v>
       </c>
       <c r="R80" t="n">
-        <v>6983126</v>
+        <v>6983219</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9522,7 +9532,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9532,7 +9542,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9543,11 +9553,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9564,10 +9569,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119788496</v>
+        <v>119789352</v>
       </c>
       <c r="B81" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9580,34 +9585,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670807</v>
+        <v>670892</v>
       </c>
       <c r="R81" t="n">
-        <v>6983126</v>
+        <v>6983131</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9639,7 +9644,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9649,7 +9654,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9681,7 +9686,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119789062</v>
+        <v>119788502</v>
       </c>
       <c r="B82" t="n">
         <v>100171</v>
@@ -9717,14 +9722,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670848</v>
+        <v>670807</v>
       </c>
       <c r="R82" t="n">
-        <v>6983160</v>
+        <v>6983126</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9756,7 +9761,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9766,7 +9771,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9777,11 +9782,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9798,10 +9798,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788716</v>
+        <v>119788561</v>
       </c>
       <c r="B83" t="n">
-        <v>91494</v>
+        <v>101074</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9814,34 +9814,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>670864</v>
+        <v>670806</v>
       </c>
       <c r="R83" t="n">
-        <v>6983129</v>
+        <v>6983157</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9915,10 +9915,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788502</v>
+        <v>119789381</v>
       </c>
       <c r="B84" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9931,34 +9931,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670807</v>
+        <v>670878</v>
       </c>
       <c r="R84" t="n">
-        <v>6983126</v>
+        <v>6983130</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10027,10 +10027,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119789399</v>
+        <v>119804612</v>
       </c>
       <c r="B85" t="n">
-        <v>91494</v>
+        <v>94311</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10043,21 +10043,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>670892</v>
+        <v>670802</v>
       </c>
       <c r="R85" t="n">
-        <v>6983131</v>
+        <v>6983219</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10139,10 +10139,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119789352</v>
+        <v>119788516</v>
       </c>
       <c r="B86" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10151,38 +10151,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670892</v>
+        <v>670807</v>
       </c>
       <c r="R86" t="n">
-        <v>6983131</v>
+        <v>6983126</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10214,7 +10219,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10224,7 +10229,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10256,10 +10261,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788402</v>
+        <v>119788496</v>
       </c>
       <c r="B87" t="n">
-        <v>91858</v>
+        <v>101074</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10268,38 +10273,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>670846</v>
+        <v>670807</v>
       </c>
       <c r="R87" t="n">
-        <v>6983191</v>
+        <v>6983126</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10331,7 +10336,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10341,12 +10346,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10378,10 +10378,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788561</v>
+        <v>119789925</v>
       </c>
       <c r="B88" t="n">
-        <v>101074</v>
+        <v>94311</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10394,34 +10394,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>670806</v>
+        <v>670884</v>
       </c>
       <c r="R88" t="n">
-        <v>6983157</v>
+        <v>6983286</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10474,11 +10474,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10495,10 +10490,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119789841</v>
+        <v>119789399</v>
       </c>
       <c r="B89" t="n">
-        <v>100080</v>
+        <v>91494</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10511,21 +10506,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10535,10 +10530,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>670817</v>
+        <v>670892</v>
       </c>
       <c r="R89" t="n">
-        <v>6983220</v>
+        <v>6983131</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10570,7 +10565,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10580,7 +10575,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10607,10 +10602,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119789381</v>
+        <v>119788716</v>
       </c>
       <c r="B90" t="n">
-        <v>100080</v>
+        <v>91494</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10623,34 +10618,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>670878</v>
+        <v>670864</v>
       </c>
       <c r="R90" t="n">
-        <v>6983130</v>
+        <v>6983129</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10682,7 +10677,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10692,7 +10687,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10703,6 +10698,11 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119899641</v>
+        <v>119898932</v>
       </c>
       <c r="B92" t="n">
-        <v>101074</v>
+        <v>94323</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10857,34 +10857,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221235</v>
+        <v>2813</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670779</v>
+        <v>670806</v>
       </c>
       <c r="R92" t="n">
-        <v>6983125</v>
+        <v>6983157</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898932</v>
+        <v>119895594</v>
       </c>
       <c r="B93" t="n">
-        <v>94323</v>
+        <v>100080</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2813</v>
+        <v>222771</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670806</v>
+        <v>670802</v>
       </c>
       <c r="R93" t="n">
-        <v>6983157</v>
+        <v>6983219</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11065,10 +11065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898558</v>
+        <v>119898656</v>
       </c>
       <c r="B94" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11081,21 +11081,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11161,6 +11161,11 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11177,10 +11182,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119899557</v>
+        <v>119898558</v>
       </c>
       <c r="B95" t="n">
-        <v>91494</v>
+        <v>100171</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11193,34 +11198,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670765</v>
+        <v>670818</v>
       </c>
       <c r="R95" t="n">
-        <v>6983124</v>
+        <v>6983189</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11252,7 +11257,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11262,7 +11267,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11289,10 +11294,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898937</v>
+        <v>119895581</v>
       </c>
       <c r="B96" t="n">
-        <v>94311</v>
+        <v>91861</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11305,34 +11310,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2809</v>
+        <v>5964</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670806</v>
+        <v>670765</v>
       </c>
       <c r="R96" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11364,7 +11369,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11374,7 +11379,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11401,10 +11406,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898984</v>
+        <v>119899557</v>
       </c>
       <c r="B97" t="n">
-        <v>94311</v>
+        <v>91494</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11417,34 +11422,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670792</v>
+        <v>670765</v>
       </c>
       <c r="R97" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11476,7 +11481,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11486,7 +11491,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11513,10 +11518,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119895594</v>
+        <v>119898913</v>
       </c>
       <c r="B98" t="n">
-        <v>100080</v>
+        <v>57326</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11525,25 +11530,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11553,10 +11558,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670802</v>
+        <v>670820</v>
       </c>
       <c r="R98" t="n">
-        <v>6983219</v>
+        <v>6983158</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11588,7 +11593,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11598,7 +11603,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11625,10 +11630,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119898758</v>
+        <v>119898663</v>
       </c>
       <c r="B99" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11641,21 +11646,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11665,10 +11670,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670804</v>
+        <v>670818</v>
       </c>
       <c r="R99" t="n">
-        <v>6983188</v>
+        <v>6983189</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11700,7 +11705,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11710,7 +11715,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11742,10 +11747,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898913</v>
+        <v>119899641</v>
       </c>
       <c r="B100" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11754,38 +11759,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670820</v>
+        <v>670779</v>
       </c>
       <c r="R100" t="n">
-        <v>6983158</v>
+        <v>6983125</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11817,7 +11822,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11827,7 +11832,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11854,10 +11859,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119898495</v>
+        <v>119900032</v>
       </c>
       <c r="B101" t="n">
-        <v>57326</v>
+        <v>100080</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11866,51 +11871,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670817</v>
+        <v>670742</v>
       </c>
       <c r="R101" t="n">
-        <v>6983220</v>
+        <v>6983030</v>
       </c>
       <c r="S101" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11939,7 +11934,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11949,7 +11944,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11976,10 +11971,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898741</v>
+        <v>119898495</v>
       </c>
       <c r="B102" t="n">
-        <v>100080</v>
+        <v>57326</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11988,41 +11983,51 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670804</v>
+        <v>670817</v>
       </c>
       <c r="R102" t="n">
-        <v>6983188</v>
+        <v>6983220</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12051,7 +12056,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12061,7 +12066,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12088,7 +12093,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119895581</v>
+        <v>119898758</v>
       </c>
       <c r="B103" t="n">
         <v>91861</v>
@@ -12124,14 +12129,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R103" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12163,7 +12168,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12173,7 +12178,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12184,6 +12189,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12200,10 +12210,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898844</v>
+        <v>119898984</v>
       </c>
       <c r="B104" t="n">
-        <v>100171</v>
+        <v>94311</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12216,21 +12226,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12240,10 +12250,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670832</v>
+        <v>670792</v>
       </c>
       <c r="R104" t="n">
-        <v>6983190</v>
+        <v>6983157</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12275,7 +12285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12285,7 +12295,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12312,7 +12322,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119899251</v>
+        <v>119898741</v>
       </c>
       <c r="B105" t="n">
         <v>100080</v>
@@ -12346,21 +12356,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670777</v>
+        <v>670804</v>
       </c>
       <c r="R105" t="n">
-        <v>6983156</v>
+        <v>6983188</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12392,7 +12397,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12402,7 +12407,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12413,11 +12418,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12434,10 +12434,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898663</v>
+        <v>119898881</v>
       </c>
       <c r="B106" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12450,21 +12450,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670818</v>
+        <v>670832</v>
       </c>
       <c r="R106" t="n">
-        <v>6983189</v>
+        <v>6983190</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12530,11 +12530,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12551,10 +12546,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119900032</v>
+        <v>119898937</v>
       </c>
       <c r="B107" t="n">
-        <v>100080</v>
+        <v>94311</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12567,34 +12562,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670742</v>
+        <v>670806</v>
       </c>
       <c r="R107" t="n">
-        <v>6983030</v>
+        <v>6983157</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12626,7 +12621,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12636,7 +12631,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12663,10 +12658,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119898656</v>
+        <v>119899251</v>
       </c>
       <c r="B108" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12679,34 +12674,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670818</v>
+        <v>670777</v>
       </c>
       <c r="R108" t="n">
-        <v>6983189</v>
+        <v>6983156</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12780,10 +12780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119898506</v>
+        <v>119899526</v>
       </c>
       <c r="B109" t="n">
-        <v>101074</v>
+        <v>104994</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12796,34 +12796,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221235</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670802</v>
+        <v>670765</v>
       </c>
       <c r="R109" t="n">
-        <v>6983219</v>
+        <v>6983124</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12855,7 +12855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12876,11 +12876,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12897,10 +12892,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119899526</v>
+        <v>119898506</v>
       </c>
       <c r="B110" t="n">
-        <v>104994</v>
+        <v>101074</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12913,34 +12908,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221725</v>
+        <v>221235</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670765</v>
+        <v>670802</v>
       </c>
       <c r="R110" t="n">
-        <v>6983124</v>
+        <v>6983219</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12972,7 +12967,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12982,7 +12977,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12993,6 +12988,11 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -9798,10 +9798,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788561</v>
+        <v>119789381</v>
       </c>
       <c r="B83" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9814,21 +9814,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9838,10 +9838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>670806</v>
+        <v>670878</v>
       </c>
       <c r="R83" t="n">
-        <v>6983157</v>
+        <v>6983130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9894,11 +9894,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9915,10 +9910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119789381</v>
+        <v>119788561</v>
       </c>
       <c r="B84" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9931,21 +9926,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9955,10 +9950,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670878</v>
+        <v>670806</v>
       </c>
       <c r="R84" t="n">
-        <v>6983130</v>
+        <v>6983157</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9990,7 +9985,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10000,7 +9995,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,6 +10006,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -6525,10 +6525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119781352</v>
+        <v>119781414</v>
       </c>
       <c r="B52" t="n">
-        <v>101074</v>
+        <v>86288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,25 +6537,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221235</v>
+        <v>426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>670782</v>
+        <v>670832</v>
       </c>
       <c r="R52" t="n">
-        <v>6983174</v>
+        <v>6983235</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781368</v>
+        <v>119781448</v>
       </c>
       <c r="B53" t="n">
-        <v>91494</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6639,25 +6639,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670847</v>
+        <v>670902</v>
       </c>
       <c r="R53" t="n">
-        <v>6983303</v>
+        <v>6983235</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119781439</v>
+        <v>119781359</v>
       </c>
       <c r="B54" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>670893</v>
+        <v>670836</v>
       </c>
       <c r="R54" t="n">
-        <v>6983206</v>
+        <v>6983189</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781414</v>
+        <v>119781361</v>
       </c>
       <c r="B55" t="n">
-        <v>86288</v>
+        <v>104996</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6843,25 +6843,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>426</v>
+        <v>224098</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670832</v>
+        <v>670789</v>
       </c>
       <c r="R55" t="n">
-        <v>6983235</v>
+        <v>6983134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6915,6 +6915,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6933,10 +6934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119781385</v>
+        <v>119781353</v>
       </c>
       <c r="B56" t="n">
-        <v>89239</v>
+        <v>101074</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6949,21 +6950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6268</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6973,10 +6974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>670900</v>
+        <v>670761</v>
       </c>
       <c r="R56" t="n">
-        <v>6983212</v>
+        <v>6983130</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7035,10 +7036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781361</v>
+        <v>119781370</v>
       </c>
       <c r="B57" t="n">
-        <v>104996</v>
+        <v>91494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7051,21 +7052,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>224098</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7075,10 +7076,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670789</v>
+        <v>670776</v>
       </c>
       <c r="R57" t="n">
-        <v>6983134</v>
+        <v>6983129</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7119,7 +7120,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781410</v>
+        <v>119781470</v>
       </c>
       <c r="B58" t="n">
-        <v>91848</v>
+        <v>100171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7150,25 +7150,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2058</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670897</v>
+        <v>670778</v>
       </c>
       <c r="R58" t="n">
-        <v>6983186</v>
+        <v>6983109</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119781353</v>
+        <v>119781392</v>
       </c>
       <c r="B59" t="n">
-        <v>101074</v>
+        <v>91850</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7252,25 +7252,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>789</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>670761</v>
+        <v>670901</v>
       </c>
       <c r="R59" t="n">
-        <v>6983130</v>
+        <v>6983185</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7342,10 +7342,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119781469</v>
+        <v>119781439</v>
       </c>
       <c r="B60" t="n">
-        <v>100171</v>
+        <v>91861</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7358,21 +7358,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670788</v>
+        <v>670893</v>
       </c>
       <c r="R60" t="n">
-        <v>6983134</v>
+        <v>6983206</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7444,10 +7444,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119781438</v>
+        <v>119781377</v>
       </c>
       <c r="B61" t="n">
-        <v>91861</v>
+        <v>57326</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7456,25 +7456,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670906</v>
+        <v>670794</v>
       </c>
       <c r="R61" t="n">
-        <v>6983256</v>
+        <v>6983144</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119781448</v>
+        <v>119781369</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>91494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7558,25 +7558,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>670902</v>
+        <v>670819</v>
       </c>
       <c r="R62" t="n">
-        <v>6983235</v>
+        <v>6983261</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119781440</v>
+        <v>119781368</v>
       </c>
       <c r="B63" t="n">
-        <v>91861</v>
+        <v>91494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7664,21 +7664,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>670899</v>
+        <v>670847</v>
       </c>
       <c r="R63" t="n">
-        <v>6983187</v>
+        <v>6983303</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7750,10 +7750,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119781377</v>
+        <v>119781348</v>
       </c>
       <c r="B64" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7762,25 +7762,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>670794</v>
+        <v>670779</v>
       </c>
       <c r="R64" t="n">
-        <v>6983144</v>
+        <v>6983126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781392</v>
+        <v>119781385</v>
       </c>
       <c r="B65" t="n">
-        <v>91850</v>
+        <v>89239</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7864,25 +7864,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>789</v>
+        <v>6268</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670901</v>
+        <v>670900</v>
       </c>
       <c r="R65" t="n">
-        <v>6983185</v>
+        <v>6983212</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781369</v>
+        <v>119781447</v>
       </c>
       <c r="B66" t="n">
-        <v>91494</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,25 +7966,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670819</v>
+        <v>670905</v>
       </c>
       <c r="R66" t="n">
-        <v>6983261</v>
+        <v>6983220</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781449</v>
+        <v>119781350</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>101074</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,25 +8068,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670901</v>
+        <v>670791</v>
       </c>
       <c r="R67" t="n">
-        <v>6983219</v>
+        <v>6983132</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781350</v>
+        <v>119781352</v>
       </c>
       <c r="B68" t="n">
         <v>101074</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670791</v>
+        <v>670782</v>
       </c>
       <c r="R68" t="n">
-        <v>6983132</v>
+        <v>6983174</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781470</v>
+        <v>119781440</v>
       </c>
       <c r="B69" t="n">
-        <v>100171</v>
+        <v>91861</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670778</v>
+        <v>670899</v>
       </c>
       <c r="R69" t="n">
-        <v>6983109</v>
+        <v>6983187</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8362,10 +8362,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119781348</v>
+        <v>119781438</v>
       </c>
       <c r="B70" t="n">
-        <v>101074</v>
+        <v>91861</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8378,21 +8378,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>670779</v>
+        <v>670906</v>
       </c>
       <c r="R70" t="n">
-        <v>6983126</v>
+        <v>6983256</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119781359</v>
+        <v>119781410</v>
       </c>
       <c r="B71" t="n">
-        <v>100080</v>
+        <v>91848</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8476,25 +8476,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222771</v>
+        <v>2058</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>670836</v>
+        <v>670897</v>
       </c>
       <c r="R71" t="n">
-        <v>6983189</v>
+        <v>6983186</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119781370</v>
+        <v>119781449</v>
       </c>
       <c r="B72" t="n">
-        <v>91494</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8578,25 +8578,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>670776</v>
+        <v>670901</v>
       </c>
       <c r="R72" t="n">
-        <v>6983129</v>
+        <v>6983219</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119781447</v>
+        <v>119781469</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>100171</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8680,25 +8680,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>670905</v>
+        <v>670788</v>
       </c>
       <c r="R73" t="n">
-        <v>6983220</v>
+        <v>6983134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119788402</v>
+        <v>119788716</v>
       </c>
       <c r="B74" t="n">
-        <v>91858</v>
+        <v>91494</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8782,38 +8782,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>670846</v>
+        <v>670864</v>
       </c>
       <c r="R74" t="n">
-        <v>6983191</v>
+        <v>6983129</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8855,12 +8855,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8874,7 +8869,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8892,10 +8887,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119789861</v>
+        <v>119789399</v>
       </c>
       <c r="B75" t="n">
-        <v>100171</v>
+        <v>91494</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8908,21 +8903,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8932,10 +8927,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>670873</v>
+        <v>670892</v>
       </c>
       <c r="R75" t="n">
-        <v>6983173</v>
+        <v>6983131</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8967,7 +8962,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8977,7 +8972,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9004,10 +8999,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119789841</v>
+        <v>119804619</v>
       </c>
       <c r="B76" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9020,21 +9015,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9044,10 +9039,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>670817</v>
+        <v>670802</v>
       </c>
       <c r="R76" t="n">
-        <v>6983220</v>
+        <v>6983219</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9079,7 +9074,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9089,7 +9084,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9116,10 +9111,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119789062</v>
+        <v>119788516</v>
       </c>
       <c r="B77" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9128,38 +9123,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>670848</v>
+        <v>670807</v>
       </c>
       <c r="R77" t="n">
-        <v>6983160</v>
+        <v>6983126</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9233,10 +9233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788949</v>
+        <v>119788496</v>
       </c>
       <c r="B78" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9249,34 +9249,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670878</v>
+        <v>670807</v>
       </c>
       <c r="R78" t="n">
-        <v>6983130</v>
+        <v>6983126</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9329,6 +9329,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9345,10 +9350,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119789631</v>
+        <v>119789841</v>
       </c>
       <c r="B79" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9361,21 +9366,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9385,10 +9390,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670906</v>
+        <v>670817</v>
       </c>
       <c r="R79" t="n">
-        <v>6983132</v>
+        <v>6983220</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9420,7 +9425,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9430,7 +9435,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9457,10 +9462,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119804619</v>
+        <v>119788402</v>
       </c>
       <c r="B80" t="n">
-        <v>100171</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9469,25 +9474,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9497,10 +9502,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>670802</v>
+        <v>670846</v>
       </c>
       <c r="R80" t="n">
-        <v>6983219</v>
+        <v>6983191</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9532,7 +9537,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9542,7 +9547,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9553,6 +9563,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9569,7 +9584,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789352</v>
+        <v>119789861</v>
       </c>
       <c r="B81" t="n">
         <v>100171</v>
@@ -9609,10 +9624,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670892</v>
+        <v>670873</v>
       </c>
       <c r="R81" t="n">
-        <v>6983131</v>
+        <v>6983173</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9644,7 +9659,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9654,7 +9669,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9665,11 +9680,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9686,7 +9696,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788502</v>
+        <v>119789062</v>
       </c>
       <c r="B82" t="n">
         <v>100171</v>
@@ -9722,14 +9732,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670807</v>
+        <v>670848</v>
       </c>
       <c r="R82" t="n">
-        <v>6983126</v>
+        <v>6983160</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9761,7 +9771,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9771,7 +9781,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9782,6 +9792,11 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9798,10 +9813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119789381</v>
+        <v>119789631</v>
       </c>
       <c r="B83" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9814,21 +9829,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9838,10 +9853,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>670878</v>
+        <v>670906</v>
       </c>
       <c r="R83" t="n">
-        <v>6983130</v>
+        <v>6983132</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9873,7 +9888,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9883,7 +9898,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9910,10 +9925,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788561</v>
+        <v>119788502</v>
       </c>
       <c r="B84" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9926,34 +9941,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670806</v>
+        <v>670807</v>
       </c>
       <c r="R84" t="n">
-        <v>6983157</v>
+        <v>6983126</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9985,7 +10000,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9995,7 +10010,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10006,11 +10021,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10027,10 +10037,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119804612</v>
+        <v>119788949</v>
       </c>
       <c r="B85" t="n">
-        <v>94311</v>
+        <v>100171</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10043,21 +10053,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10067,10 +10077,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>670802</v>
+        <v>670878</v>
       </c>
       <c r="R85" t="n">
-        <v>6983219</v>
+        <v>6983130</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10102,7 +10112,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10112,7 +10122,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10139,10 +10149,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788516</v>
+        <v>119788561</v>
       </c>
       <c r="B86" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10151,43 +10161,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670807</v>
+        <v>670806</v>
       </c>
       <c r="R86" t="n">
-        <v>6983126</v>
+        <v>6983157</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10219,7 +10224,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10229,7 +10234,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10261,10 +10266,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788496</v>
+        <v>119789352</v>
       </c>
       <c r="B87" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10277,34 +10282,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>670807</v>
+        <v>670892</v>
       </c>
       <c r="R87" t="n">
-        <v>6983126</v>
+        <v>6983131</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10336,7 +10341,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10346,7 +10351,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10378,7 +10383,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119789925</v>
+        <v>119804612</v>
       </c>
       <c r="B88" t="n">
         <v>94311</v>
@@ -10414,14 +10419,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>670884</v>
+        <v>670802</v>
       </c>
       <c r="R88" t="n">
-        <v>6983286</v>
+        <v>6983219</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10453,7 +10458,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10463,7 +10468,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10490,10 +10495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119789399</v>
+        <v>119804779</v>
       </c>
       <c r="B89" t="n">
-        <v>91494</v>
+        <v>94311</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10506,34 +10511,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>670892</v>
+        <v>670884</v>
       </c>
       <c r="R89" t="n">
-        <v>6983131</v>
+        <v>6983286</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10565,7 +10570,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10575,7 +10580,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10602,10 +10607,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119788716</v>
+        <v>119789381</v>
       </c>
       <c r="B90" t="n">
-        <v>91494</v>
+        <v>100080</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10618,34 +10623,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>670864</v>
+        <v>670878</v>
       </c>
       <c r="R90" t="n">
-        <v>6983129</v>
+        <v>6983130</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10677,7 +10682,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10687,7 +10692,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10698,11 +10703,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119898932</v>
+        <v>119899641</v>
       </c>
       <c r="B92" t="n">
-        <v>94323</v>
+        <v>101074</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10857,34 +10857,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2813</v>
+        <v>221235</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670806</v>
+        <v>670779</v>
       </c>
       <c r="R92" t="n">
-        <v>6983157</v>
+        <v>6983125</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119895594</v>
+        <v>119898506</v>
       </c>
       <c r="B93" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11049,6 +11049,11 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11065,10 +11070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898656</v>
+        <v>119898669</v>
       </c>
       <c r="B94" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11081,21 +11086,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11182,10 +11187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898558</v>
+        <v>119898758</v>
       </c>
       <c r="B95" t="n">
-        <v>100171</v>
+        <v>91861</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11198,21 +11203,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11222,10 +11227,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670818</v>
+        <v>670804</v>
       </c>
       <c r="R95" t="n">
-        <v>6983189</v>
+        <v>6983188</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11257,7 +11262,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11267,7 +11272,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11278,6 +11283,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11294,10 +11304,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119895581</v>
+        <v>119898495</v>
       </c>
       <c r="B96" t="n">
-        <v>91861</v>
+        <v>57326</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11306,41 +11316,51 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670765</v>
+        <v>670817</v>
       </c>
       <c r="R96" t="n">
-        <v>6983124</v>
+        <v>6983220</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11369,7 +11389,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11379,7 +11399,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11518,10 +11538,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119898913</v>
+        <v>119900032</v>
       </c>
       <c r="B98" t="n">
-        <v>57326</v>
+        <v>100080</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11530,38 +11550,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670820</v>
+        <v>670742</v>
       </c>
       <c r="R98" t="n">
-        <v>6983158</v>
+        <v>6983030</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11593,7 +11613,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11603,7 +11623,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11630,10 +11650,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119898663</v>
+        <v>119898844</v>
       </c>
       <c r="B99" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11646,21 +11666,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11670,10 +11690,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670818</v>
+        <v>670832</v>
       </c>
       <c r="R99" t="n">
-        <v>6983189</v>
+        <v>6983190</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11705,7 +11725,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11715,7 +11735,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11726,11 +11746,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11747,10 +11762,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119899641</v>
+        <v>119898937</v>
       </c>
       <c r="B100" t="n">
-        <v>101074</v>
+        <v>94311</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11763,34 +11778,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670779</v>
+        <v>670806</v>
       </c>
       <c r="R100" t="n">
-        <v>6983125</v>
+        <v>6983157</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11822,7 +11837,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11832,7 +11847,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11859,10 +11874,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119900032</v>
+        <v>119895581</v>
       </c>
       <c r="B101" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11875,34 +11890,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670742</v>
+        <v>670765</v>
       </c>
       <c r="R101" t="n">
-        <v>6983030</v>
+        <v>6983124</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11934,7 +11949,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11944,7 +11959,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11971,10 +11986,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898495</v>
+        <v>119898741</v>
       </c>
       <c r="B102" t="n">
-        <v>57326</v>
+        <v>100080</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11983,51 +11998,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670817</v>
+        <v>670804</v>
       </c>
       <c r="R102" t="n">
-        <v>6983220</v>
+        <v>6983188</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12056,7 +12061,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12066,7 +12071,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12093,10 +12098,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119898758</v>
+        <v>119895594</v>
       </c>
       <c r="B103" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12109,21 +12114,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12133,10 +12138,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670804</v>
+        <v>670802</v>
       </c>
       <c r="R103" t="n">
-        <v>6983188</v>
+        <v>6983219</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12168,7 +12173,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12178,7 +12183,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12189,11 +12194,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12210,10 +12210,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898984</v>
+        <v>119898663</v>
       </c>
       <c r="B104" t="n">
-        <v>94311</v>
+        <v>100080</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12226,21 +12226,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2809</v>
+        <v>222771</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670792</v>
+        <v>670818</v>
       </c>
       <c r="R104" t="n">
-        <v>6983157</v>
+        <v>6983189</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12306,6 +12306,11 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12322,10 +12327,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119898741</v>
+        <v>119898913</v>
       </c>
       <c r="B105" t="n">
-        <v>100080</v>
+        <v>57326</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12334,25 +12339,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12362,10 +12367,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670804</v>
+        <v>670820</v>
       </c>
       <c r="R105" t="n">
-        <v>6983188</v>
+        <v>6983158</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12397,7 +12402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12407,7 +12412,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12434,10 +12439,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898881</v>
+        <v>119898932</v>
       </c>
       <c r="B106" t="n">
-        <v>100171</v>
+        <v>94323</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12450,21 +12455,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12474,10 +12479,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670832</v>
+        <v>670806</v>
       </c>
       <c r="R106" t="n">
-        <v>6983190</v>
+        <v>6983157</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12509,7 +12514,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12519,7 +12524,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12546,10 +12551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119898937</v>
+        <v>119899251</v>
       </c>
       <c r="B107" t="n">
-        <v>94311</v>
+        <v>100080</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12562,34 +12567,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2809</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670806</v>
+        <v>670777</v>
       </c>
       <c r="R107" t="n">
-        <v>6983157</v>
+        <v>6983156</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12621,7 +12631,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12631,7 +12641,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12642,6 +12652,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12658,10 +12673,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119899251</v>
+        <v>119899526</v>
       </c>
       <c r="B108" t="n">
-        <v>100080</v>
+        <v>104994</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12674,39 +12689,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222771</v>
+        <v>221725</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670777</v>
+        <v>670765</v>
       </c>
       <c r="R108" t="n">
-        <v>6983156</v>
+        <v>6983124</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12738,7 +12748,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12748,7 +12758,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12759,11 +12769,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12780,10 +12785,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119899526</v>
+        <v>119898656</v>
       </c>
       <c r="B109" t="n">
-        <v>104994</v>
+        <v>101074</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12796,34 +12801,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>221235</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670765</v>
+        <v>670818</v>
       </c>
       <c r="R109" t="n">
-        <v>6983124</v>
+        <v>6983189</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12855,7 +12860,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12865,7 +12870,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12876,6 +12881,11 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12892,10 +12902,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119898506</v>
+        <v>119898984</v>
       </c>
       <c r="B110" t="n">
-        <v>101074</v>
+        <v>94311</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12908,21 +12918,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12932,10 +12942,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670802</v>
+        <v>670792</v>
       </c>
       <c r="R110" t="n">
-        <v>6983219</v>
+        <v>6983157</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12967,7 +12977,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12977,7 +12987,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12988,11 +12998,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7036,10 +7036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781370</v>
+        <v>119781470</v>
       </c>
       <c r="B57" t="n">
-        <v>91494</v>
+        <v>100171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7052,21 +7052,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670776</v>
+        <v>670778</v>
       </c>
       <c r="R57" t="n">
-        <v>6983129</v>
+        <v>6983109</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781470</v>
+        <v>119781370</v>
       </c>
       <c r="B58" t="n">
-        <v>100171</v>
+        <v>91494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670778</v>
+        <v>670776</v>
       </c>
       <c r="R58" t="n">
-        <v>6983109</v>
+        <v>6983129</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781385</v>
+        <v>119781447</v>
       </c>
       <c r="B65" t="n">
-        <v>89239</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7864,25 +7864,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6268</v>
+        <v>4368</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670900</v>
+        <v>670905</v>
       </c>
       <c r="R65" t="n">
-        <v>6983212</v>
+        <v>6983220</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781447</v>
+        <v>119781350</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>101074</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,25 +7966,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670905</v>
+        <v>670791</v>
       </c>
       <c r="R66" t="n">
-        <v>6983220</v>
+        <v>6983132</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781350</v>
+        <v>119781385</v>
       </c>
       <c r="B67" t="n">
-        <v>101074</v>
+        <v>89239</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8072,21 +8072,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>6268</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670791</v>
+        <v>670900</v>
       </c>
       <c r="R67" t="n">
-        <v>6983132</v>
+        <v>6983212</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9233,10 +9233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788496</v>
+        <v>119789861</v>
       </c>
       <c r="B78" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9249,34 +9249,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670807</v>
+        <v>670873</v>
       </c>
       <c r="R78" t="n">
-        <v>6983126</v>
+        <v>6983173</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9329,11 +9329,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9350,10 +9345,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119789841</v>
+        <v>119788496</v>
       </c>
       <c r="B79" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9366,34 +9361,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670817</v>
+        <v>670807</v>
       </c>
       <c r="R79" t="n">
-        <v>6983220</v>
+        <v>6983126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9425,7 +9420,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9435,7 +9430,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9446,6 +9441,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9584,10 +9584,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789861</v>
+        <v>119789841</v>
       </c>
       <c r="B81" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670873</v>
+        <v>670817</v>
       </c>
       <c r="R81" t="n">
-        <v>6983173</v>
+        <v>6983220</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898506</v>
+        <v>119898669</v>
       </c>
       <c r="B93" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670802</v>
+        <v>670818</v>
       </c>
       <c r="R93" t="n">
-        <v>6983219</v>
+        <v>6983189</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11070,10 +11070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898669</v>
+        <v>119898506</v>
       </c>
       <c r="B94" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11086,21 +11086,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R94" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11187,10 +11187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898758</v>
+        <v>119900032</v>
       </c>
       <c r="B95" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11203,34 +11203,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670804</v>
+        <v>670742</v>
       </c>
       <c r="R95" t="n">
-        <v>6983188</v>
+        <v>6983030</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11283,11 +11283,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11304,10 +11299,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898495</v>
+        <v>119899557</v>
       </c>
       <c r="B96" t="n">
-        <v>57326</v>
+        <v>91494</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11316,51 +11311,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670817</v>
+        <v>670765</v>
       </c>
       <c r="R96" t="n">
-        <v>6983220</v>
+        <v>6983124</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11389,7 +11374,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11399,7 +11384,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11426,10 +11411,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119899557</v>
+        <v>119898495</v>
       </c>
       <c r="B97" t="n">
-        <v>91494</v>
+        <v>57326</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11438,41 +11423,51 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670765</v>
+        <v>670817</v>
       </c>
       <c r="R97" t="n">
-        <v>6983124</v>
+        <v>6983220</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11501,7 +11496,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11511,7 +11506,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11538,10 +11533,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119900032</v>
+        <v>119898758</v>
       </c>
       <c r="B98" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11554,34 +11549,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670742</v>
+        <v>670804</v>
       </c>
       <c r="R98" t="n">
-        <v>6983030</v>
+        <v>6983188</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11613,7 +11608,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11623,7 +11618,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11634,6 +11629,11 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13012,6 +13012,1026 @@
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>120235121</v>
+      </c>
+      <c r="B111" t="n">
+        <v>100080</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>670816</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6983123</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120235196</v>
+      </c>
+      <c r="B112" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>670779</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6983095</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120235198</v>
+      </c>
+      <c r="B113" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>670732</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6983014</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120235118</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91494</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>670878</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6983125</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120235111</v>
+      </c>
+      <c r="B115" t="n">
+        <v>101074</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>670748</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6982992</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120235122</v>
+      </c>
+      <c r="B116" t="n">
+        <v>100080</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>670768</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6983085</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120235119</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91494</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>670847</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6983132</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120235197</v>
+      </c>
+      <c r="B118" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>670768</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6983085</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120235194</v>
+      </c>
+      <c r="B119" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>670904</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6983156</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120235195</v>
+      </c>
+      <c r="B120" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>670813</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6983126</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -7852,10 +7852,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781447</v>
+        <v>119781385</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>89239</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7864,25 +7864,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4368</v>
+        <v>6268</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670905</v>
+        <v>670900</v>
       </c>
       <c r="R65" t="n">
-        <v>6983220</v>
+        <v>6983212</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781350</v>
+        <v>119781447</v>
       </c>
       <c r="B66" t="n">
-        <v>101074</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,25 +7966,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670791</v>
+        <v>670905</v>
       </c>
       <c r="R66" t="n">
-        <v>6983132</v>
+        <v>6983220</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781385</v>
+        <v>119781350</v>
       </c>
       <c r="B67" t="n">
-        <v>89239</v>
+        <v>101074</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8072,21 +8072,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6268</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670900</v>
+        <v>670791</v>
       </c>
       <c r="R67" t="n">
-        <v>6983212</v>
+        <v>6983132</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9233,10 +9233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119789861</v>
+        <v>119788496</v>
       </c>
       <c r="B78" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9249,34 +9249,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670873</v>
+        <v>670807</v>
       </c>
       <c r="R78" t="n">
-        <v>6983173</v>
+        <v>6983126</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9329,6 +9329,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9345,10 +9350,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788496</v>
+        <v>119789841</v>
       </c>
       <c r="B79" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9361,34 +9366,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670807</v>
+        <v>670817</v>
       </c>
       <c r="R79" t="n">
-        <v>6983126</v>
+        <v>6983220</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9420,7 +9425,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9430,7 +9435,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9441,11 +9446,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9584,10 +9584,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789841</v>
+        <v>119789861</v>
       </c>
       <c r="B81" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670817</v>
+        <v>670873</v>
       </c>
       <c r="R81" t="n">
-        <v>6983220</v>
+        <v>6983173</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898669</v>
+        <v>119898506</v>
       </c>
       <c r="B93" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R93" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11070,10 +11070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898506</v>
+        <v>119898669</v>
       </c>
       <c r="B94" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11086,21 +11086,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670802</v>
+        <v>670818</v>
       </c>
       <c r="R94" t="n">
-        <v>6983219</v>
+        <v>6983189</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11187,10 +11187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119900032</v>
+        <v>119898758</v>
       </c>
       <c r="B95" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11203,34 +11203,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670742</v>
+        <v>670804</v>
       </c>
       <c r="R95" t="n">
-        <v>6983030</v>
+        <v>6983188</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11283,6 +11283,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11299,10 +11304,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119899557</v>
+        <v>119898495</v>
       </c>
       <c r="B96" t="n">
-        <v>91494</v>
+        <v>57326</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11311,41 +11316,51 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670765</v>
+        <v>670817</v>
       </c>
       <c r="R96" t="n">
-        <v>6983124</v>
+        <v>6983220</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11374,7 +11389,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11384,7 +11399,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11411,10 +11426,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898495</v>
+        <v>119899557</v>
       </c>
       <c r="B97" t="n">
-        <v>57326</v>
+        <v>91494</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11423,51 +11438,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670817</v>
+        <v>670765</v>
       </c>
       <c r="R97" t="n">
-        <v>6983220</v>
+        <v>6983124</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11496,7 +11501,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11506,7 +11511,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11533,10 +11538,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119898758</v>
+        <v>119900032</v>
       </c>
       <c r="B98" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11549,34 +11554,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670804</v>
+        <v>670742</v>
       </c>
       <c r="R98" t="n">
-        <v>6983188</v>
+        <v>6983030</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11608,7 +11613,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11618,7 +11623,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11629,11 +11634,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -9233,10 +9233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788496</v>
+        <v>119789861</v>
       </c>
       <c r="B78" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9249,34 +9249,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670807</v>
+        <v>670873</v>
       </c>
       <c r="R78" t="n">
-        <v>6983126</v>
+        <v>6983173</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9329,11 +9329,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9350,10 +9345,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119789841</v>
+        <v>119788496</v>
       </c>
       <c r="B79" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9366,34 +9361,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670817</v>
+        <v>670807</v>
       </c>
       <c r="R79" t="n">
-        <v>6983220</v>
+        <v>6983126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9425,7 +9420,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9435,7 +9430,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9446,6 +9441,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9584,10 +9584,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789861</v>
+        <v>119789841</v>
       </c>
       <c r="B81" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670873</v>
+        <v>670817</v>
       </c>
       <c r="R81" t="n">
-        <v>6983173</v>
+        <v>6983220</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898506</v>
+        <v>119898669</v>
       </c>
       <c r="B93" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670802</v>
+        <v>670818</v>
       </c>
       <c r="R93" t="n">
-        <v>6983219</v>
+        <v>6983189</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11070,10 +11070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898669</v>
+        <v>119898506</v>
       </c>
       <c r="B94" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11086,21 +11086,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R94" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -9233,10 +9233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119789861</v>
+        <v>119788496</v>
       </c>
       <c r="B78" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9249,34 +9249,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670873</v>
+        <v>670807</v>
       </c>
       <c r="R78" t="n">
-        <v>6983173</v>
+        <v>6983126</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9329,6 +9329,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9345,10 +9350,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788496</v>
+        <v>119789841</v>
       </c>
       <c r="B79" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9361,34 +9366,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670807</v>
+        <v>670817</v>
       </c>
       <c r="R79" t="n">
-        <v>6983126</v>
+        <v>6983220</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9420,7 +9425,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9430,7 +9435,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9441,11 +9446,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9584,10 +9584,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789841</v>
+        <v>119789861</v>
       </c>
       <c r="B81" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670817</v>
+        <v>670873</v>
       </c>
       <c r="R81" t="n">
-        <v>6983220</v>
+        <v>6983173</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11187,10 +11187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898758</v>
+        <v>119900032</v>
       </c>
       <c r="B95" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11203,34 +11203,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670804</v>
+        <v>670742</v>
       </c>
       <c r="R95" t="n">
-        <v>6983188</v>
+        <v>6983030</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11283,11 +11283,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11304,10 +11299,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898495</v>
+        <v>119899557</v>
       </c>
       <c r="B96" t="n">
-        <v>57326</v>
+        <v>91494</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11316,51 +11311,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670817</v>
+        <v>670765</v>
       </c>
       <c r="R96" t="n">
-        <v>6983220</v>
+        <v>6983124</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11389,7 +11374,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11399,7 +11384,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11426,10 +11411,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119899557</v>
+        <v>119898495</v>
       </c>
       <c r="B97" t="n">
-        <v>91494</v>
+        <v>57326</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11438,41 +11423,51 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670765</v>
+        <v>670817</v>
       </c>
       <c r="R97" t="n">
-        <v>6983124</v>
+        <v>6983220</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11501,7 +11496,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11511,7 +11506,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11538,10 +11533,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119900032</v>
+        <v>119898758</v>
       </c>
       <c r="B98" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11554,34 +11549,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670742</v>
+        <v>670804</v>
       </c>
       <c r="R98" t="n">
-        <v>6983030</v>
+        <v>6983188</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11613,7 +11608,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11623,7 +11618,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11634,6 +11629,11 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898669</v>
+        <v>119898506</v>
       </c>
       <c r="B93" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R93" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11070,10 +11070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898506</v>
+        <v>119898669</v>
       </c>
       <c r="B94" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11086,21 +11086,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670802</v>
+        <v>670818</v>
       </c>
       <c r="R94" t="n">
-        <v>6983219</v>
+        <v>6983189</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -6525,10 +6525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119781414</v>
+        <v>119781369</v>
       </c>
       <c r="B52" t="n">
-        <v>86288</v>
+        <v>91512</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,25 +6537,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>426</v>
+        <v>4769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>670832</v>
+        <v>670819</v>
       </c>
       <c r="R52" t="n">
-        <v>6983235</v>
+        <v>6983261</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781448</v>
+        <v>119781368</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>91512</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6639,25 +6639,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670902</v>
+        <v>670847</v>
       </c>
       <c r="R53" t="n">
-        <v>6983235</v>
+        <v>6983303</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6732,7 +6732,7 @@
         <v>119781359</v>
       </c>
       <c r="B54" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781361</v>
+        <v>119781385</v>
       </c>
       <c r="B55" t="n">
-        <v>104996</v>
+        <v>89256</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6847,21 +6847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>224098</v>
+        <v>6268</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670789</v>
+        <v>670900</v>
       </c>
       <c r="R55" t="n">
-        <v>6983134</v>
+        <v>6983212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6915,7 +6915,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6934,10 +6933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119781353</v>
+        <v>119781448</v>
       </c>
       <c r="B56" t="n">
-        <v>101074</v>
+        <v>91876</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6946,25 +6945,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6974,10 +6973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>670761</v>
+        <v>670902</v>
       </c>
       <c r="R56" t="n">
-        <v>6983130</v>
+        <v>6983235</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7036,10 +7035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781470</v>
+        <v>119781392</v>
       </c>
       <c r="B57" t="n">
-        <v>100171</v>
+        <v>91868</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7048,25 +7047,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>789</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7076,10 +7075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670778</v>
+        <v>670901</v>
       </c>
       <c r="R57" t="n">
-        <v>6983109</v>
+        <v>6983185</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7138,10 +7137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781370</v>
+        <v>119781414</v>
       </c>
       <c r="B58" t="n">
-        <v>91494</v>
+        <v>86305</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7150,25 +7149,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4769</v>
+        <v>426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7178,10 +7177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670776</v>
+        <v>670832</v>
       </c>
       <c r="R58" t="n">
-        <v>6983129</v>
+        <v>6983235</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7240,10 +7239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119781392</v>
+        <v>119781449</v>
       </c>
       <c r="B59" t="n">
-        <v>91850</v>
+        <v>91876</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7252,25 +7251,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>789</v>
+        <v>4368</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7283,7 +7282,7 @@
         <v>670901</v>
       </c>
       <c r="R59" t="n">
-        <v>6983185</v>
+        <v>6983219</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7342,10 +7341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119781439</v>
+        <v>119781377</v>
       </c>
       <c r="B60" t="n">
-        <v>91861</v>
+        <v>57336</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7354,25 +7353,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7382,10 +7381,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670893</v>
+        <v>670794</v>
       </c>
       <c r="R60" t="n">
-        <v>6983206</v>
+        <v>6983144</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7444,10 +7443,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119781377</v>
+        <v>119781440</v>
       </c>
       <c r="B61" t="n">
-        <v>57326</v>
+        <v>91879</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7456,25 +7455,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7484,10 +7483,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670794</v>
+        <v>670899</v>
       </c>
       <c r="R61" t="n">
-        <v>6983144</v>
+        <v>6983187</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,10 +7545,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119781369</v>
+        <v>119781361</v>
       </c>
       <c r="B62" t="n">
-        <v>91494</v>
+        <v>105019</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7562,21 +7561,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4769</v>
+        <v>224098</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7586,10 +7585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>670819</v>
+        <v>670789</v>
       </c>
       <c r="R62" t="n">
-        <v>6983261</v>
+        <v>6983134</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7630,6 +7629,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119781368</v>
+        <v>119781353</v>
       </c>
       <c r="B63" t="n">
-        <v>91494</v>
+        <v>101097</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7664,21 +7664,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>670847</v>
+        <v>670761</v>
       </c>
       <c r="R63" t="n">
-        <v>6983303</v>
+        <v>6983130</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7750,10 +7750,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119781348</v>
+        <v>119781439</v>
       </c>
       <c r="B64" t="n">
-        <v>101074</v>
+        <v>91879</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7766,21 +7766,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>670779</v>
+        <v>670893</v>
       </c>
       <c r="R64" t="n">
-        <v>6983126</v>
+        <v>6983206</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781385</v>
+        <v>119781410</v>
       </c>
       <c r="B65" t="n">
-        <v>89239</v>
+        <v>91866</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7864,25 +7864,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6268</v>
+        <v>2058</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670900</v>
+        <v>670897</v>
       </c>
       <c r="R65" t="n">
-        <v>6983212</v>
+        <v>6983186</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781447</v>
+        <v>119781350</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>101097</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,25 +7966,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670905</v>
+        <v>670791</v>
       </c>
       <c r="R66" t="n">
-        <v>6983220</v>
+        <v>6983132</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781350</v>
+        <v>119781469</v>
       </c>
       <c r="B67" t="n">
-        <v>101074</v>
+        <v>100194</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8072,21 +8072,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670791</v>
+        <v>670788</v>
       </c>
       <c r="R67" t="n">
-        <v>6983132</v>
+        <v>6983134</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781352</v>
+        <v>119781438</v>
       </c>
       <c r="B68" t="n">
-        <v>101074</v>
+        <v>91879</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670782</v>
+        <v>670906</v>
       </c>
       <c r="R68" t="n">
-        <v>6983174</v>
+        <v>6983256</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781440</v>
+        <v>119781470</v>
       </c>
       <c r="B69" t="n">
-        <v>91861</v>
+        <v>100194</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670899</v>
+        <v>670778</v>
       </c>
       <c r="R69" t="n">
-        <v>6983187</v>
+        <v>6983109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8362,10 +8362,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119781438</v>
+        <v>119781352</v>
       </c>
       <c r="B70" t="n">
-        <v>91861</v>
+        <v>101097</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8378,21 +8378,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>670906</v>
+        <v>670782</v>
       </c>
       <c r="R70" t="n">
-        <v>6983256</v>
+        <v>6983174</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119781410</v>
+        <v>119781447</v>
       </c>
       <c r="B71" t="n">
-        <v>91848</v>
+        <v>91876</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8476,25 +8476,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2058</v>
+        <v>4368</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>670897</v>
+        <v>670905</v>
       </c>
       <c r="R71" t="n">
-        <v>6983186</v>
+        <v>6983220</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119781449</v>
+        <v>119781348</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>101097</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8578,25 +8578,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>670901</v>
+        <v>670779</v>
       </c>
       <c r="R72" t="n">
-        <v>6983219</v>
+        <v>6983126</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119781469</v>
+        <v>119781370</v>
       </c>
       <c r="B73" t="n">
-        <v>100171</v>
+        <v>91512</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8684,21 +8684,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>670788</v>
+        <v>670776</v>
       </c>
       <c r="R73" t="n">
-        <v>6983134</v>
+        <v>6983129</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8773,7 +8773,7 @@
         <v>119788716</v>
       </c>
       <c r="B74" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8887,10 +8887,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119789399</v>
+        <v>119804779</v>
       </c>
       <c r="B75" t="n">
-        <v>91494</v>
+        <v>94334</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8903,34 +8903,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>670892</v>
+        <v>670884</v>
       </c>
       <c r="R75" t="n">
-        <v>6983131</v>
+        <v>6983286</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8999,10 +8999,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119804619</v>
+        <v>119789841</v>
       </c>
       <c r="B76" t="n">
-        <v>100171</v>
+        <v>100103</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9015,21 +9015,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>670802</v>
+        <v>670817</v>
       </c>
       <c r="R76" t="n">
-        <v>6983219</v>
+        <v>6983220</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9111,10 +9111,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788516</v>
+        <v>119789062</v>
       </c>
       <c r="B77" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9123,43 +9123,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>670807</v>
+        <v>670848</v>
       </c>
       <c r="R77" t="n">
-        <v>6983126</v>
+        <v>6983160</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9191,7 +9186,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9201,7 +9196,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9233,10 +9228,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788496</v>
+        <v>119789381</v>
       </c>
       <c r="B78" t="n">
-        <v>101074</v>
+        <v>100103</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9249,34 +9244,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670807</v>
+        <v>670878</v>
       </c>
       <c r="R78" t="n">
-        <v>6983126</v>
+        <v>6983130</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9308,7 +9303,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9318,7 +9313,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9329,11 +9324,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9350,10 +9340,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119789841</v>
+        <v>119804612</v>
       </c>
       <c r="B79" t="n">
-        <v>100080</v>
+        <v>94334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9366,21 +9356,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9390,10 +9380,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670817</v>
+        <v>670802</v>
       </c>
       <c r="R79" t="n">
-        <v>6983220</v>
+        <v>6983219</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9425,7 +9415,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9435,7 +9425,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9462,10 +9452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788402</v>
+        <v>119804619</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>100194</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9474,25 +9464,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9502,10 +9492,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>670846</v>
+        <v>670802</v>
       </c>
       <c r="R80" t="n">
-        <v>6983191</v>
+        <v>6983219</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9537,7 +9527,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9547,12 +9537,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9563,11 +9548,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9584,10 +9564,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789861</v>
+        <v>119789352</v>
       </c>
       <c r="B81" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9624,10 +9604,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670873</v>
+        <v>670892</v>
       </c>
       <c r="R81" t="n">
-        <v>6983173</v>
+        <v>6983131</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9659,7 +9639,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9669,7 +9649,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9680,6 +9660,11 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9696,10 +9681,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119789062</v>
+        <v>119788561</v>
       </c>
       <c r="B82" t="n">
-        <v>100171</v>
+        <v>101097</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9712,21 +9697,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9736,10 +9721,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670848</v>
+        <v>670806</v>
       </c>
       <c r="R82" t="n">
-        <v>6983160</v>
+        <v>6983157</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9771,7 +9756,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9781,7 +9766,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9816,7 +9801,7 @@
         <v>119789631</v>
       </c>
       <c r="B83" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9925,10 +9910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788502</v>
+        <v>119788402</v>
       </c>
       <c r="B84" t="n">
-        <v>100171</v>
+        <v>91876</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9937,38 +9922,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670807</v>
+        <v>670846</v>
       </c>
       <c r="R84" t="n">
-        <v>6983126</v>
+        <v>6983191</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10000,7 +9985,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10010,7 +9995,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10021,6 +10011,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10040,7 +10035,7 @@
         <v>119788949</v>
       </c>
       <c r="B85" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10149,10 +10144,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788561</v>
+        <v>119788496</v>
       </c>
       <c r="B86" t="n">
-        <v>101074</v>
+        <v>101097</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10185,14 +10180,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670806</v>
+        <v>670807</v>
       </c>
       <c r="R86" t="n">
-        <v>6983157</v>
+        <v>6983126</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10224,7 +10219,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10234,7 +10229,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10266,10 +10261,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119789352</v>
+        <v>119788502</v>
       </c>
       <c r="B87" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10302,14 +10297,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>670892</v>
+        <v>670807</v>
       </c>
       <c r="R87" t="n">
-        <v>6983131</v>
+        <v>6983126</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10341,7 +10336,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10351,7 +10346,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10362,11 +10357,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10383,10 +10373,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119804612</v>
+        <v>119788516</v>
       </c>
       <c r="B88" t="n">
-        <v>94311</v>
+        <v>57336</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10395,38 +10385,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>670802</v>
+        <v>670807</v>
       </c>
       <c r="R88" t="n">
-        <v>6983219</v>
+        <v>6983126</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10458,7 +10453,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10468,7 +10463,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10479,6 +10474,11 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10495,10 +10495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119804779</v>
+        <v>119789861</v>
       </c>
       <c r="B89" t="n">
-        <v>94311</v>
+        <v>100194</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10511,34 +10511,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>670884</v>
+        <v>670873</v>
       </c>
       <c r="R89" t="n">
-        <v>6983286</v>
+        <v>6983173</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10607,10 +10607,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119789381</v>
+        <v>119789399</v>
       </c>
       <c r="B90" t="n">
-        <v>100080</v>
+        <v>91512</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10623,21 +10623,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>670878</v>
+        <v>670892</v>
       </c>
       <c r="R90" t="n">
-        <v>6983130</v>
+        <v>6983131</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10722,7 +10722,7 @@
         <v>119842147</v>
       </c>
       <c r="B91" t="n">
-        <v>104996</v>
+        <v>105019</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119899641</v>
+        <v>119899557</v>
       </c>
       <c r="B92" t="n">
-        <v>101074</v>
+        <v>91512</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670779</v>
+        <v>670765</v>
       </c>
       <c r="R92" t="n">
-        <v>6983125</v>
+        <v>6983124</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898506</v>
+        <v>119895594</v>
       </c>
       <c r="B93" t="n">
-        <v>101074</v>
+        <v>100103</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11049,11 +11049,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11070,10 +11065,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898669</v>
+        <v>119898932</v>
       </c>
       <c r="B94" t="n">
-        <v>100171</v>
+        <v>94346</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11086,21 +11081,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11110,10 +11105,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670818</v>
+        <v>670806</v>
       </c>
       <c r="R94" t="n">
-        <v>6983189</v>
+        <v>6983157</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11145,7 +11140,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11150,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11166,11 +11161,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11187,10 +11177,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119900032</v>
+        <v>119898741</v>
       </c>
       <c r="B95" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11223,14 +11213,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670742</v>
+        <v>670804</v>
       </c>
       <c r="R95" t="n">
-        <v>6983030</v>
+        <v>6983188</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11262,7 +11252,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11272,7 +11262,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11299,10 +11289,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119899557</v>
+        <v>119899641</v>
       </c>
       <c r="B96" t="n">
-        <v>91494</v>
+        <v>101097</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11315,21 +11305,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11339,10 +11329,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670765</v>
+        <v>670779</v>
       </c>
       <c r="R96" t="n">
-        <v>6983124</v>
+        <v>6983125</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11411,10 +11401,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898495</v>
+        <v>119898913</v>
       </c>
       <c r="B97" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11445,29 +11435,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670817</v>
+        <v>670820</v>
       </c>
       <c r="R97" t="n">
-        <v>6983220</v>
+        <v>6983158</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11496,7 +11476,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11506,7 +11486,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11533,10 +11513,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119898758</v>
+        <v>119899251</v>
       </c>
       <c r="B98" t="n">
-        <v>91861</v>
+        <v>100103</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11549,34 +11529,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670804</v>
+        <v>670777</v>
       </c>
       <c r="R98" t="n">
-        <v>6983188</v>
+        <v>6983156</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11608,7 +11593,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11618,7 +11603,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11650,10 +11635,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119898844</v>
+        <v>119899526</v>
       </c>
       <c r="B99" t="n">
-        <v>100171</v>
+        <v>105017</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11666,34 +11651,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670832</v>
+        <v>670765</v>
       </c>
       <c r="R99" t="n">
-        <v>6983190</v>
+        <v>6983124</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11725,7 +11710,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11735,7 +11720,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11762,10 +11747,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898937</v>
+        <v>119898656</v>
       </c>
       <c r="B100" t="n">
-        <v>94311</v>
+        <v>101097</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11778,21 +11763,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11802,10 +11787,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670806</v>
+        <v>670818</v>
       </c>
       <c r="R100" t="n">
-        <v>6983157</v>
+        <v>6983189</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11837,7 +11822,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11847,7 +11832,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11858,6 +11843,11 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11877,7 +11867,7 @@
         <v>119895581</v>
       </c>
       <c r="B101" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11986,10 +11976,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898741</v>
+        <v>119898758</v>
       </c>
       <c r="B102" t="n">
-        <v>100080</v>
+        <v>91879</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12002,21 +11992,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12061,7 +12051,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12071,7 +12061,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12082,6 +12072,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12098,10 +12093,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119895594</v>
+        <v>119900032</v>
       </c>
       <c r="B103" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12134,14 +12129,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670802</v>
+        <v>670742</v>
       </c>
       <c r="R103" t="n">
-        <v>6983219</v>
+        <v>6983030</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12173,7 +12168,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12183,7 +12178,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12210,10 +12205,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898663</v>
+        <v>119898506</v>
       </c>
       <c r="B104" t="n">
-        <v>100080</v>
+        <v>101097</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12226,21 +12221,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12250,10 +12245,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R104" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12285,7 +12280,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12295,7 +12290,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12327,10 +12322,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119898913</v>
+        <v>119898669</v>
       </c>
       <c r="B105" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12339,25 +12334,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12367,10 +12362,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670820</v>
+        <v>670818</v>
       </c>
       <c r="R105" t="n">
-        <v>6983158</v>
+        <v>6983189</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12402,7 +12397,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12412,7 +12407,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12423,6 +12418,11 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12439,10 +12439,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898932</v>
+        <v>119898937</v>
       </c>
       <c r="B106" t="n">
-        <v>94323</v>
+        <v>94334</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12455,21 +12455,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119899251</v>
+        <v>119898495</v>
       </c>
       <c r="B107" t="n">
-        <v>100080</v>
+        <v>57336</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12563,31 +12563,36 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12596,13 +12601,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670777</v>
+        <v>670817</v>
       </c>
       <c r="R107" t="n">
-        <v>6983156</v>
+        <v>6983220</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12631,7 +12636,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12641,7 +12646,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12652,11 +12657,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12673,10 +12673,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119899526</v>
+        <v>119898663</v>
       </c>
       <c r="B108" t="n">
-        <v>104994</v>
+        <v>100103</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12689,34 +12689,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>222771</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670765</v>
+        <v>670818</v>
       </c>
       <c r="R108" t="n">
-        <v>6983124</v>
+        <v>6983189</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12769,6 +12769,11 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12785,10 +12790,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119898656</v>
+        <v>119898844</v>
       </c>
       <c r="B109" t="n">
-        <v>101074</v>
+        <v>100194</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12801,21 +12806,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12825,10 +12830,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670818</v>
+        <v>670832</v>
       </c>
       <c r="R109" t="n">
-        <v>6983189</v>
+        <v>6983190</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12860,7 +12865,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12870,7 +12875,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12881,11 +12886,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12905,7 +12905,7 @@
         <v>119898984</v>
       </c>
       <c r="B110" t="n">
-        <v>94311</v>
+        <v>94334</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13014,10 +13014,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235121</v>
+        <v>120235194</v>
       </c>
       <c r="B111" t="n">
-        <v>100080</v>
+        <v>100194</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13030,21 +13030,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670816</v>
+        <v>670904</v>
       </c>
       <c r="R111" t="n">
-        <v>6983123</v>
+        <v>6983156</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13116,10 +13116,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235196</v>
+        <v>120235195</v>
       </c>
       <c r="B112" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>670779</v>
+        <v>670813</v>
       </c>
       <c r="R112" t="n">
-        <v>6983095</v>
+        <v>6983126</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13218,10 +13218,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235198</v>
+        <v>120235119</v>
       </c>
       <c r="B113" t="n">
-        <v>100171</v>
+        <v>91512</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13234,21 +13234,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670732</v>
+        <v>670847</v>
       </c>
       <c r="R113" t="n">
-        <v>6983014</v>
+        <v>6983132</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235118</v>
+        <v>120235122</v>
       </c>
       <c r="B114" t="n">
-        <v>91494</v>
+        <v>100103</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670878</v>
+        <v>670768</v>
       </c>
       <c r="R114" t="n">
-        <v>6983125</v>
+        <v>6983085</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,10 +13422,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235111</v>
+        <v>120235118</v>
       </c>
       <c r="B115" t="n">
-        <v>101074</v>
+        <v>91512</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670748</v>
+        <v>670878</v>
       </c>
       <c r="R115" t="n">
-        <v>6982992</v>
+        <v>6983125</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235122</v>
+        <v>120235111</v>
       </c>
       <c r="B116" t="n">
-        <v>100080</v>
+        <v>101097</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13540,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670768</v>
+        <v>670748</v>
       </c>
       <c r="R116" t="n">
-        <v>6983085</v>
+        <v>6982992</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,10 +13626,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235119</v>
+        <v>120235121</v>
       </c>
       <c r="B117" t="n">
-        <v>91494</v>
+        <v>100103</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13642,21 +13642,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670847</v>
+        <v>670816</v>
       </c>
       <c r="R117" t="n">
-        <v>6983132</v>
+        <v>6983123</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13728,10 +13728,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235197</v>
+        <v>120235196</v>
       </c>
       <c r="B118" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670768</v>
+        <v>670779</v>
       </c>
       <c r="R118" t="n">
-        <v>6983085</v>
+        <v>6983095</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235194</v>
+        <v>120235197</v>
       </c>
       <c r="B119" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>670904</v>
+        <v>670768</v>
       </c>
       <c r="R119" t="n">
-        <v>6983156</v>
+        <v>6983085</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13932,10 +13932,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235195</v>
+        <v>120235198</v>
       </c>
       <c r="B120" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670813</v>
+        <v>670732</v>
       </c>
       <c r="R120" t="n">
-        <v>6983126</v>
+        <v>6983014</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -11747,10 +11747,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898656</v>
+        <v>119895581</v>
       </c>
       <c r="B100" t="n">
-        <v>101097</v>
+        <v>91879</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11763,34 +11763,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670818</v>
+        <v>670765</v>
       </c>
       <c r="R100" t="n">
-        <v>6983189</v>
+        <v>6983124</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11843,11 +11843,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11864,7 +11859,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119895581</v>
+        <v>119898758</v>
       </c>
       <c r="B101" t="n">
         <v>91879</v>
@@ -11900,14 +11895,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R101" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11939,7 +11934,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11949,7 +11944,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11960,6 +11955,11 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898758</v>
+        <v>119898656</v>
       </c>
       <c r="B102" t="n">
-        <v>91879</v>
+        <v>101097</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11992,21 +11992,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670804</v>
+        <v>670818</v>
       </c>
       <c r="R102" t="n">
-        <v>6983188</v>
+        <v>6983189</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13218,10 +13218,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235119</v>
+        <v>120235122</v>
       </c>
       <c r="B113" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13234,21 +13234,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670847</v>
+        <v>670768</v>
       </c>
       <c r="R113" t="n">
-        <v>6983132</v>
+        <v>6983085</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235122</v>
+        <v>120235119</v>
       </c>
       <c r="B114" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670768</v>
+        <v>670847</v>
       </c>
       <c r="R114" t="n">
-        <v>6983085</v>
+        <v>6983132</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -6525,10 +6525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119781369</v>
+        <v>119781377</v>
       </c>
       <c r="B52" t="n">
-        <v>91512</v>
+        <v>57336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,25 +6537,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>670819</v>
+        <v>670794</v>
       </c>
       <c r="R52" t="n">
-        <v>6983261</v>
+        <v>6983144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,7 +6627,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781368</v>
+        <v>119781369</v>
       </c>
       <c r="B53" t="n">
         <v>91512</v>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670847</v>
+        <v>670819</v>
       </c>
       <c r="R53" t="n">
-        <v>6983303</v>
+        <v>6983261</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119781359</v>
+        <v>119781469</v>
       </c>
       <c r="B54" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>670836</v>
+        <v>670788</v>
       </c>
       <c r="R54" t="n">
-        <v>6983189</v>
+        <v>6983134</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781385</v>
+        <v>119781350</v>
       </c>
       <c r="B55" t="n">
-        <v>89256</v>
+        <v>101097</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6847,21 +6847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6268</v>
+        <v>221235</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670900</v>
+        <v>670791</v>
       </c>
       <c r="R55" t="n">
-        <v>6983212</v>
+        <v>6983132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119781448</v>
+        <v>119781392</v>
       </c>
       <c r="B56" t="n">
-        <v>91876</v>
+        <v>91868</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6945,25 +6945,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4368</v>
+        <v>789</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>670902</v>
+        <v>670901</v>
       </c>
       <c r="R56" t="n">
-        <v>6983235</v>
+        <v>6983185</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781392</v>
+        <v>119781438</v>
       </c>
       <c r="B57" t="n">
-        <v>91868</v>
+        <v>91879</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7047,25 +7047,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>789</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670901</v>
+        <v>670906</v>
       </c>
       <c r="R57" t="n">
-        <v>6983185</v>
+        <v>6983256</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781414</v>
+        <v>119781352</v>
       </c>
       <c r="B58" t="n">
-        <v>86305</v>
+        <v>101097</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7149,25 +7149,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>426</v>
+        <v>221235</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670832</v>
+        <v>670782</v>
       </c>
       <c r="R58" t="n">
-        <v>6983235</v>
+        <v>6983174</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119781449</v>
+        <v>119781470</v>
       </c>
       <c r="B59" t="n">
-        <v>91876</v>
+        <v>100194</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7251,25 +7251,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>670901</v>
+        <v>670778</v>
       </c>
       <c r="R59" t="n">
-        <v>6983219</v>
+        <v>6983109</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119781377</v>
+        <v>119781447</v>
       </c>
       <c r="B60" t="n">
-        <v>57336</v>
+        <v>91876</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7357,21 +7357,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>4368</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670794</v>
+        <v>670905</v>
       </c>
       <c r="R60" t="n">
-        <v>6983144</v>
+        <v>6983220</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119781440</v>
+        <v>119781385</v>
       </c>
       <c r="B61" t="n">
-        <v>91879</v>
+        <v>89256</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>6268</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670899</v>
+        <v>670900</v>
       </c>
       <c r="R61" t="n">
-        <v>6983187</v>
+        <v>6983212</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,10 +7545,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119781361</v>
+        <v>119781348</v>
       </c>
       <c r="B62" t="n">
-        <v>105019</v>
+        <v>101097</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7561,21 +7561,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>224098</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7585,10 +7585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>670789</v>
+        <v>670779</v>
       </c>
       <c r="R62" t="n">
-        <v>6983134</v>
+        <v>6983126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7629,7 +7629,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7648,10 +7647,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119781353</v>
+        <v>119781414</v>
       </c>
       <c r="B63" t="n">
-        <v>101097</v>
+        <v>86305</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7660,25 +7659,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221235</v>
+        <v>426</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7688,10 +7687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>670761</v>
+        <v>670832</v>
       </c>
       <c r="R63" t="n">
-        <v>6983130</v>
+        <v>6983235</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7750,7 +7749,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119781439</v>
+        <v>119781440</v>
       </c>
       <c r="B64" t="n">
         <v>91879</v>
@@ -7790,10 +7789,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>670893</v>
+        <v>670899</v>
       </c>
       <c r="R64" t="n">
-        <v>6983206</v>
+        <v>6983187</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7852,10 +7851,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781410</v>
+        <v>119781439</v>
       </c>
       <c r="B65" t="n">
-        <v>91866</v>
+        <v>91879</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7864,25 +7863,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2058</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7892,10 +7891,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670897</v>
+        <v>670893</v>
       </c>
       <c r="R65" t="n">
-        <v>6983186</v>
+        <v>6983206</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7954,10 +7953,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781350</v>
+        <v>119781449</v>
       </c>
       <c r="B66" t="n">
-        <v>101097</v>
+        <v>91876</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,25 +7965,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7994,10 +7993,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670791</v>
+        <v>670901</v>
       </c>
       <c r="R66" t="n">
-        <v>6983132</v>
+        <v>6983219</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8056,10 +8055,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781469</v>
+        <v>119781368</v>
       </c>
       <c r="B67" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8072,21 +8071,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8096,10 +8095,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670788</v>
+        <v>670847</v>
       </c>
       <c r="R67" t="n">
-        <v>6983134</v>
+        <v>6983303</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,10 +8157,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781438</v>
+        <v>119781359</v>
       </c>
       <c r="B68" t="n">
-        <v>91879</v>
+        <v>100103</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8174,21 +8173,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8198,10 +8197,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670906</v>
+        <v>670836</v>
       </c>
       <c r="R68" t="n">
-        <v>6983256</v>
+        <v>6983189</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8260,10 +8259,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781470</v>
+        <v>119781353</v>
       </c>
       <c r="B69" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,21 +8275,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8299,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670778</v>
+        <v>670761</v>
       </c>
       <c r="R69" t="n">
-        <v>6983109</v>
+        <v>6983130</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8362,10 +8361,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119781352</v>
+        <v>119781361</v>
       </c>
       <c r="B70" t="n">
-        <v>101097</v>
+        <v>105019</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8378,21 +8377,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221235</v>
+        <v>224098</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8402,10 +8401,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>670782</v>
+        <v>670789</v>
       </c>
       <c r="R70" t="n">
-        <v>6983174</v>
+        <v>6983134</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8446,6 +8445,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119781447</v>
+        <v>119781370</v>
       </c>
       <c r="B71" t="n">
-        <v>91876</v>
+        <v>91512</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8476,25 +8476,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>670905</v>
+        <v>670776</v>
       </c>
       <c r="R71" t="n">
-        <v>6983220</v>
+        <v>6983129</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119781348</v>
+        <v>119781448</v>
       </c>
       <c r="B72" t="n">
-        <v>101097</v>
+        <v>91876</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8578,25 +8578,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>670779</v>
+        <v>670902</v>
       </c>
       <c r="R72" t="n">
-        <v>6983126</v>
+        <v>6983235</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119781370</v>
+        <v>119781410</v>
       </c>
       <c r="B73" t="n">
-        <v>91512</v>
+        <v>91866</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8680,25 +8680,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>2058</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>670776</v>
+        <v>670897</v>
       </c>
       <c r="R73" t="n">
-        <v>6983129</v>
+        <v>6983186</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119788716</v>
+        <v>119789631</v>
       </c>
       <c r="B74" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8786,34 +8786,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>670864</v>
+        <v>670906</v>
       </c>
       <c r="R74" t="n">
-        <v>6983129</v>
+        <v>6983132</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8866,11 +8866,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8887,10 +8882,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119804779</v>
+        <v>119789861</v>
       </c>
       <c r="B75" t="n">
-        <v>94334</v>
+        <v>100194</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8903,34 +8898,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>670884</v>
+        <v>670873</v>
       </c>
       <c r="R75" t="n">
-        <v>6983286</v>
+        <v>6983173</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8962,7 +8957,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8972,7 +8967,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9111,7 +9106,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119789062</v>
+        <v>119788949</v>
       </c>
       <c r="B77" t="n">
         <v>100194</v>
@@ -9151,10 +9146,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>670848</v>
+        <v>670878</v>
       </c>
       <c r="R77" t="n">
-        <v>6983160</v>
+        <v>6983130</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9186,7 +9181,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9196,7 +9191,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9207,11 +9202,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9340,10 +9330,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119804612</v>
+        <v>119788502</v>
       </c>
       <c r="B79" t="n">
-        <v>94334</v>
+        <v>100194</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9356,34 +9346,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670802</v>
+        <v>670807</v>
       </c>
       <c r="R79" t="n">
-        <v>6983219</v>
+        <v>6983126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9415,7 +9405,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9425,7 +9415,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9452,10 +9442,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119804619</v>
+        <v>119788561</v>
       </c>
       <c r="B80" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9468,21 +9458,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9492,10 +9482,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>670802</v>
+        <v>670806</v>
       </c>
       <c r="R80" t="n">
-        <v>6983219</v>
+        <v>6983157</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9527,7 +9517,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9537,7 +9527,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9548,6 +9538,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9564,10 +9559,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119789352</v>
+        <v>119788402</v>
       </c>
       <c r="B81" t="n">
-        <v>100194</v>
+        <v>91876</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9576,25 +9571,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9604,10 +9599,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670892</v>
+        <v>670846</v>
       </c>
       <c r="R81" t="n">
-        <v>6983131</v>
+        <v>6983191</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9639,7 +9634,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9649,7 +9644,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788561</v>
+        <v>119789925</v>
       </c>
       <c r="B82" t="n">
-        <v>101097</v>
+        <v>94334</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9697,34 +9697,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670806</v>
+        <v>670884</v>
       </c>
       <c r="R82" t="n">
-        <v>6983157</v>
+        <v>6983286</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9777,11 +9777,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9798,7 +9793,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119789631</v>
+        <v>119804619</v>
       </c>
       <c r="B83" t="n">
         <v>100194</v>
@@ -9838,10 +9833,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>670906</v>
+        <v>670802</v>
       </c>
       <c r="R83" t="n">
-        <v>6983132</v>
+        <v>6983219</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9873,7 +9868,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9883,7 +9878,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9910,10 +9905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788402</v>
+        <v>119789352</v>
       </c>
       <c r="B84" t="n">
-        <v>91876</v>
+        <v>100194</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9922,25 +9917,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9950,10 +9945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670846</v>
+        <v>670892</v>
       </c>
       <c r="R84" t="n">
-        <v>6983191</v>
+        <v>6983131</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9985,7 +9980,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9995,12 +9990,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10014,7 +10004,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10032,10 +10022,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788949</v>
+        <v>119789399</v>
       </c>
       <c r="B85" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10048,21 +10038,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10072,10 +10062,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>670878</v>
+        <v>670892</v>
       </c>
       <c r="R85" t="n">
-        <v>6983130</v>
+        <v>6983131</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10107,7 +10097,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10117,7 +10107,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10144,10 +10134,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788496</v>
+        <v>119789062</v>
       </c>
       <c r="B86" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10160,34 +10150,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670807</v>
+        <v>670848</v>
       </c>
       <c r="R86" t="n">
-        <v>6983126</v>
+        <v>6983160</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10219,7 +10209,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10229,7 +10219,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10261,10 +10251,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788502</v>
+        <v>119788516</v>
       </c>
       <c r="B87" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10273,28 +10263,33 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
@@ -10357,6 +10352,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10373,10 +10373,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788516</v>
+        <v>119788716</v>
       </c>
       <c r="B88" t="n">
-        <v>57336</v>
+        <v>91512</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10385,43 +10385,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>670807</v>
+        <v>670864</v>
       </c>
       <c r="R88" t="n">
-        <v>6983126</v>
+        <v>6983129</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10453,7 +10448,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10463,7 +10458,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10495,10 +10490,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119789861</v>
+        <v>119804612</v>
       </c>
       <c r="B89" t="n">
-        <v>100194</v>
+        <v>94334</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10511,21 +10506,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10535,10 +10530,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>670873</v>
+        <v>670802</v>
       </c>
       <c r="R89" t="n">
-        <v>6983173</v>
+        <v>6983219</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10570,7 +10565,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10580,7 +10575,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10607,10 +10602,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119789399</v>
+        <v>119788496</v>
       </c>
       <c r="B90" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10623,34 +10618,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>670892</v>
+        <v>670807</v>
       </c>
       <c r="R90" t="n">
-        <v>6983131</v>
+        <v>6983126</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10682,7 +10677,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10692,7 +10687,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10703,6 +10698,11 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119899557</v>
+        <v>119898937</v>
       </c>
       <c r="B92" t="n">
-        <v>91512</v>
+        <v>94334</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10857,34 +10857,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670765</v>
+        <v>670806</v>
       </c>
       <c r="R92" t="n">
-        <v>6983124</v>
+        <v>6983157</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119895594</v>
+        <v>119898656</v>
       </c>
       <c r="B93" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670802</v>
+        <v>670818</v>
       </c>
       <c r="R93" t="n">
-        <v>6983219</v>
+        <v>6983189</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11049,6 +11049,11 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11065,10 +11070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898932</v>
+        <v>119898844</v>
       </c>
       <c r="B94" t="n">
-        <v>94346</v>
+        <v>100194</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11081,21 +11086,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11105,10 +11110,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670806</v>
+        <v>670832</v>
       </c>
       <c r="R94" t="n">
-        <v>6983157</v>
+        <v>6983190</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11140,7 +11145,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11150,7 +11155,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11177,7 +11182,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898741</v>
+        <v>119895594</v>
       </c>
       <c r="B95" t="n">
         <v>100103</v>
@@ -11217,10 +11222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670804</v>
+        <v>670802</v>
       </c>
       <c r="R95" t="n">
-        <v>6983188</v>
+        <v>6983219</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11252,7 +11257,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11262,7 +11267,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11289,7 +11294,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119899641</v>
+        <v>119898506</v>
       </c>
       <c r="B96" t="n">
         <v>101097</v>
@@ -11325,14 +11330,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670779</v>
+        <v>670802</v>
       </c>
       <c r="R96" t="n">
-        <v>6983125</v>
+        <v>6983219</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11364,7 +11369,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11374,7 +11379,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11385,6 +11390,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11401,10 +11411,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898913</v>
+        <v>119899641</v>
       </c>
       <c r="B97" t="n">
-        <v>57336</v>
+        <v>101097</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11413,38 +11423,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670820</v>
+        <v>670779</v>
       </c>
       <c r="R97" t="n">
-        <v>6983158</v>
+        <v>6983125</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11476,7 +11486,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11486,7 +11496,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11513,10 +11523,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119899251</v>
+        <v>119898758</v>
       </c>
       <c r="B98" t="n">
-        <v>100103</v>
+        <v>91879</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11529,39 +11539,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670777</v>
+        <v>670804</v>
       </c>
       <c r="R98" t="n">
-        <v>6983156</v>
+        <v>6983188</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11593,7 +11598,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11603,7 +11608,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11635,10 +11640,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119899526</v>
+        <v>119898741</v>
       </c>
       <c r="B99" t="n">
-        <v>105017</v>
+        <v>100103</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11651,34 +11656,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221725</v>
+        <v>222771</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R99" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11710,7 +11715,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11720,7 +11725,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11747,10 +11752,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119895581</v>
+        <v>119898558</v>
       </c>
       <c r="B100" t="n">
-        <v>91879</v>
+        <v>100194</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11763,34 +11768,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670765</v>
+        <v>670818</v>
       </c>
       <c r="R100" t="n">
-        <v>6983124</v>
+        <v>6983189</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11822,7 +11827,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11832,7 +11837,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11859,10 +11864,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119898758</v>
+        <v>119898984</v>
       </c>
       <c r="B101" t="n">
-        <v>91879</v>
+        <v>94334</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11875,21 +11880,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5964</v>
+        <v>2809</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11899,10 +11904,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670804</v>
+        <v>670792</v>
       </c>
       <c r="R101" t="n">
-        <v>6983188</v>
+        <v>6983157</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11934,7 +11939,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11944,7 +11949,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11955,11 +11960,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898656</v>
+        <v>119899526</v>
       </c>
       <c r="B102" t="n">
-        <v>101097</v>
+        <v>105017</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11992,34 +11992,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221235</v>
+        <v>221725</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670818</v>
+        <v>670765</v>
       </c>
       <c r="R102" t="n">
-        <v>6983189</v>
+        <v>6983124</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12072,11 +12072,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12093,7 +12088,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119900032</v>
+        <v>119899251</v>
       </c>
       <c r="B103" t="n">
         <v>100103</v>
@@ -12127,16 +12122,21 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670742</v>
+        <v>670777</v>
       </c>
       <c r="R103" t="n">
-        <v>6983030</v>
+        <v>6983156</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12189,6 +12189,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12205,10 +12210,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898506</v>
+        <v>119900032</v>
       </c>
       <c r="B104" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12221,34 +12226,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670802</v>
+        <v>670742</v>
       </c>
       <c r="R104" t="n">
-        <v>6983219</v>
+        <v>6983030</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12280,7 +12285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12290,7 +12295,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12301,11 +12306,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12322,10 +12322,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119898669</v>
+        <v>119899557</v>
       </c>
       <c r="B105" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12338,34 +12338,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670818</v>
+        <v>670765</v>
       </c>
       <c r="R105" t="n">
-        <v>6983189</v>
+        <v>6983124</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12418,11 +12418,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12439,10 +12434,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898937</v>
+        <v>119898495</v>
       </c>
       <c r="B106" t="n">
-        <v>94334</v>
+        <v>57336</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12451,41 +12446,51 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670806</v>
+        <v>670817</v>
       </c>
       <c r="R106" t="n">
-        <v>6983157</v>
+        <v>6983220</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12514,7 +12519,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12524,7 +12529,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12551,7 +12556,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119898495</v>
+        <v>119898913</v>
       </c>
       <c r="B107" t="n">
         <v>57336</v>
@@ -12585,29 +12590,19 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670817</v>
+        <v>670820</v>
       </c>
       <c r="R107" t="n">
-        <v>6983220</v>
+        <v>6983158</v>
       </c>
       <c r="S107" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12636,7 +12631,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12646,7 +12641,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12790,10 +12785,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119898844</v>
+        <v>119895581</v>
       </c>
       <c r="B109" t="n">
-        <v>100194</v>
+        <v>91879</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12806,34 +12801,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670832</v>
+        <v>670765</v>
       </c>
       <c r="R109" t="n">
-        <v>6983190</v>
+        <v>6983124</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12865,7 +12860,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12875,7 +12870,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12902,10 +12897,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119898984</v>
+        <v>119898932</v>
       </c>
       <c r="B110" t="n">
-        <v>94334</v>
+        <v>94346</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12918,21 +12913,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12942,7 +12937,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670792</v>
+        <v>670806</v>
       </c>
       <c r="R110" t="n">
         <v>6983157</v>
@@ -12977,7 +12972,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12987,7 +12982,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13014,10 +13009,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235194</v>
+        <v>120235119</v>
       </c>
       <c r="B111" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13030,21 +13025,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13054,10 +13049,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670904</v>
+        <v>670847</v>
       </c>
       <c r="R111" t="n">
-        <v>6983156</v>
+        <v>6983132</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13116,10 +13111,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235195</v>
+        <v>120235111</v>
       </c>
       <c r="B112" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13132,21 +13127,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13156,10 +13151,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>670813</v>
+        <v>670748</v>
       </c>
       <c r="R112" t="n">
-        <v>6983126</v>
+        <v>6982992</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13218,10 +13213,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235122</v>
+        <v>120235198</v>
       </c>
       <c r="B113" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13234,21 +13229,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13258,10 +13253,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670768</v>
+        <v>670732</v>
       </c>
       <c r="R113" t="n">
-        <v>6983085</v>
+        <v>6983014</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,10 +13315,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235119</v>
+        <v>120235121</v>
       </c>
       <c r="B114" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13331,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13355,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670847</v>
+        <v>670816</v>
       </c>
       <c r="R114" t="n">
-        <v>6983132</v>
+        <v>6983123</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,10 +13417,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235118</v>
+        <v>120235197</v>
       </c>
       <c r="B115" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13438,21 +13433,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13462,10 +13457,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670878</v>
+        <v>670768</v>
       </c>
       <c r="R115" t="n">
-        <v>6983125</v>
+        <v>6983085</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13519,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235111</v>
+        <v>120235118</v>
       </c>
       <c r="B116" t="n">
-        <v>101097</v>
+        <v>91512</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13535,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13559,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670748</v>
+        <v>670878</v>
       </c>
       <c r="R116" t="n">
-        <v>6982992</v>
+        <v>6983125</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,10 +13621,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235121</v>
+        <v>120235196</v>
       </c>
       <c r="B117" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13642,21 +13637,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13666,10 +13661,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670816</v>
+        <v>670779</v>
       </c>
       <c r="R117" t="n">
-        <v>6983123</v>
+        <v>6983095</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13728,7 +13723,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235196</v>
+        <v>120235195</v>
       </c>
       <c r="B118" t="n">
         <v>100194</v>
@@ -13768,10 +13763,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670779</v>
+        <v>670813</v>
       </c>
       <c r="R118" t="n">
-        <v>6983095</v>
+        <v>6983126</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13830,10 +13825,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235197</v>
+        <v>120235122</v>
       </c>
       <c r="B119" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13846,21 +13841,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13932,7 +13927,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235198</v>
+        <v>120235194</v>
       </c>
       <c r="B120" t="n">
         <v>100194</v>
@@ -13972,10 +13967,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670732</v>
+        <v>670904</v>
       </c>
       <c r="R120" t="n">
-        <v>6983014</v>
+        <v>6983156</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -9905,10 +9905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119789352</v>
+        <v>119789399</v>
       </c>
       <c r="B84" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10001,11 +10001,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10022,10 +10017,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119789399</v>
+        <v>119789352</v>
       </c>
       <c r="B85" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10038,21 +10033,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10097,7 +10092,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10107,7 +10102,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10118,6 +10113,11 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119898937</v>
+        <v>119898669</v>
       </c>
       <c r="B92" t="n">
-        <v>94334</v>
+        <v>100194</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670806</v>
+        <v>670818</v>
       </c>
       <c r="R92" t="n">
-        <v>6983157</v>
+        <v>6983189</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10937,6 +10937,11 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11070,10 +11075,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898844</v>
+        <v>119899526</v>
       </c>
       <c r="B94" t="n">
-        <v>100194</v>
+        <v>105017</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11086,34 +11091,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670832</v>
+        <v>670765</v>
       </c>
       <c r="R94" t="n">
-        <v>6983190</v>
+        <v>6983124</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11145,7 +11150,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11160,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11182,10 +11187,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119895594</v>
+        <v>119899641</v>
       </c>
       <c r="B95" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11198,34 +11203,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670802</v>
+        <v>670779</v>
       </c>
       <c r="R95" t="n">
-        <v>6983219</v>
+        <v>6983125</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11257,7 +11262,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11267,7 +11272,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11294,10 +11299,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898506</v>
+        <v>119898495</v>
       </c>
       <c r="B96" t="n">
-        <v>101097</v>
+        <v>57336</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11306,41 +11311,51 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670802</v>
+        <v>670817</v>
       </c>
       <c r="R96" t="n">
-        <v>6983219</v>
+        <v>6983220</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11369,7 +11384,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11379,7 +11394,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11390,11 +11405,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11411,10 +11421,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119899641</v>
+        <v>119898932</v>
       </c>
       <c r="B97" t="n">
-        <v>101097</v>
+        <v>94346</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11427,34 +11437,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221235</v>
+        <v>2813</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670779</v>
+        <v>670806</v>
       </c>
       <c r="R97" t="n">
-        <v>6983125</v>
+        <v>6983157</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11486,7 +11496,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11496,7 +11506,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11523,10 +11533,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119898758</v>
+        <v>119898913</v>
       </c>
       <c r="B98" t="n">
-        <v>91879</v>
+        <v>57336</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11535,25 +11545,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11563,10 +11573,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670804</v>
+        <v>670820</v>
       </c>
       <c r="R98" t="n">
-        <v>6983188</v>
+        <v>6983158</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11598,7 +11608,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11608,7 +11618,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11619,11 +11629,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11640,10 +11645,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119898741</v>
+        <v>119898758</v>
       </c>
       <c r="B99" t="n">
-        <v>100103</v>
+        <v>91879</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11656,21 +11661,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11715,7 +11720,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11725,7 +11730,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11736,6 +11741,11 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11752,10 +11762,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898558</v>
+        <v>119898506</v>
       </c>
       <c r="B100" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11768,21 +11778,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11792,10 +11802,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R100" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11848,6 +11858,11 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11864,10 +11879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119898984</v>
+        <v>119898844</v>
       </c>
       <c r="B101" t="n">
-        <v>94334</v>
+        <v>100194</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11880,21 +11895,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11904,10 +11919,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670792</v>
+        <v>670832</v>
       </c>
       <c r="R101" t="n">
-        <v>6983157</v>
+        <v>6983190</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11939,7 +11954,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11949,7 +11964,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11976,10 +11991,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119899526</v>
+        <v>119898741</v>
       </c>
       <c r="B102" t="n">
-        <v>105017</v>
+        <v>100103</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11992,34 +12007,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221725</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R102" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12051,7 +12066,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12061,7 +12076,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12088,10 +12103,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119899251</v>
+        <v>119898937</v>
       </c>
       <c r="B103" t="n">
-        <v>100103</v>
+        <v>94334</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12104,39 +12119,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670777</v>
+        <v>670806</v>
       </c>
       <c r="R103" t="n">
-        <v>6983156</v>
+        <v>6983157</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12168,7 +12178,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12178,7 +12188,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12189,11 +12199,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12210,10 +12215,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119900032</v>
+        <v>119898984</v>
       </c>
       <c r="B104" t="n">
-        <v>100103</v>
+        <v>94334</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12226,34 +12231,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670742</v>
+        <v>670792</v>
       </c>
       <c r="R104" t="n">
-        <v>6983030</v>
+        <v>6983157</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12285,7 +12290,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12295,7 +12300,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12434,10 +12439,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898495</v>
+        <v>119900032</v>
       </c>
       <c r="B106" t="n">
-        <v>57336</v>
+        <v>100103</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12446,51 +12451,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670817</v>
+        <v>670742</v>
       </c>
       <c r="R106" t="n">
-        <v>6983220</v>
+        <v>6983030</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12519,7 +12514,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12529,7 +12524,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12556,10 +12551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119898913</v>
+        <v>119895581</v>
       </c>
       <c r="B107" t="n">
-        <v>57336</v>
+        <v>91879</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12568,38 +12563,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670820</v>
+        <v>670765</v>
       </c>
       <c r="R107" t="n">
-        <v>6983158</v>
+        <v>6983124</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12631,7 +12626,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12641,7 +12636,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12785,10 +12780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119895581</v>
+        <v>119899251</v>
       </c>
       <c r="B109" t="n">
-        <v>91879</v>
+        <v>100103</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12801,34 +12796,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670765</v>
+        <v>670777</v>
       </c>
       <c r="R109" t="n">
-        <v>6983124</v>
+        <v>6983156</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12881,6 +12881,11 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12897,10 +12902,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119898932</v>
+        <v>119895594</v>
       </c>
       <c r="B110" t="n">
-        <v>94346</v>
+        <v>100103</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12913,21 +12918,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2813</v>
+        <v>222771</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12937,10 +12942,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670806</v>
+        <v>670802</v>
       </c>
       <c r="R110" t="n">
-        <v>6983157</v>
+        <v>6983219</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12972,7 +12977,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12982,7 +12987,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13009,10 +13014,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235119</v>
+        <v>120235197</v>
       </c>
       <c r="B111" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13025,21 +13030,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13049,10 +13054,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670847</v>
+        <v>670768</v>
       </c>
       <c r="R111" t="n">
-        <v>6983132</v>
+        <v>6983085</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13213,10 +13218,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235198</v>
+        <v>120235119</v>
       </c>
       <c r="B113" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13229,21 +13234,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13253,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670732</v>
+        <v>670847</v>
       </c>
       <c r="R113" t="n">
-        <v>6983014</v>
+        <v>6983132</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13315,10 +13320,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235121</v>
+        <v>120235118</v>
       </c>
       <c r="B114" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13331,21 +13336,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13355,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670816</v>
+        <v>670878</v>
       </c>
       <c r="R114" t="n">
-        <v>6983123</v>
+        <v>6983125</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13417,7 +13422,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235197</v>
+        <v>120235194</v>
       </c>
       <c r="B115" t="n">
         <v>100194</v>
@@ -13457,10 +13462,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670768</v>
+        <v>670904</v>
       </c>
       <c r="R115" t="n">
-        <v>6983085</v>
+        <v>6983156</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13519,10 +13524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235118</v>
+        <v>120235122</v>
       </c>
       <c r="B116" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13535,21 +13540,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13559,10 +13564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670878</v>
+        <v>670768</v>
       </c>
       <c r="R116" t="n">
-        <v>6983125</v>
+        <v>6983085</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13621,7 +13626,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235196</v>
+        <v>120235198</v>
       </c>
       <c r="B117" t="n">
         <v>100194</v>
@@ -13661,10 +13666,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670779</v>
+        <v>670732</v>
       </c>
       <c r="R117" t="n">
-        <v>6983095</v>
+        <v>6983014</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13723,7 +13728,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235195</v>
+        <v>120235196</v>
       </c>
       <c r="B118" t="n">
         <v>100194</v>
@@ -13763,10 +13768,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670813</v>
+        <v>670779</v>
       </c>
       <c r="R118" t="n">
-        <v>6983126</v>
+        <v>6983095</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13825,7 +13830,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235122</v>
+        <v>120235121</v>
       </c>
       <c r="B119" t="n">
         <v>100103</v>
@@ -13865,10 +13870,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>670768</v>
+        <v>670816</v>
       </c>
       <c r="R119" t="n">
-        <v>6983085</v>
+        <v>6983123</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13927,7 +13932,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235194</v>
+        <v>120235195</v>
       </c>
       <c r="B120" t="n">
         <v>100194</v>
@@ -13967,10 +13972,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670904</v>
+        <v>670813</v>
       </c>
       <c r="R120" t="n">
-        <v>6983156</v>
+        <v>6983126</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -12103,10 +12103,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119898937</v>
+        <v>119899557</v>
       </c>
       <c r="B103" t="n">
-        <v>94334</v>
+        <v>91512</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12119,34 +12119,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670806</v>
+        <v>670765</v>
       </c>
       <c r="R103" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12215,7 +12215,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898984</v>
+        <v>119898937</v>
       </c>
       <c r="B104" t="n">
         <v>94334</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670792</v>
+        <v>670806</v>
       </c>
       <c r="R104" t="n">
         <v>6983157</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12327,10 +12327,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119899557</v>
+        <v>119898984</v>
       </c>
       <c r="B105" t="n">
-        <v>91512</v>
+        <v>94334</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12343,34 +12343,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670765</v>
+        <v>670792</v>
       </c>
       <c r="R105" t="n">
-        <v>6983124</v>
+        <v>6983157</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -10958,10 +10958,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898656</v>
+        <v>119898495</v>
       </c>
       <c r="B93" t="n">
-        <v>101097</v>
+        <v>57336</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10970,41 +10970,51 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670818</v>
+        <v>670817</v>
       </c>
       <c r="R93" t="n">
-        <v>6983189</v>
+        <v>6983220</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11033,7 +11043,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11043,7 +11053,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11054,11 +11064,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11075,10 +11080,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119899526</v>
+        <v>119898656</v>
       </c>
       <c r="B94" t="n">
-        <v>105017</v>
+        <v>101097</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11091,34 +11096,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>221235</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670765</v>
+        <v>670818</v>
       </c>
       <c r="R94" t="n">
-        <v>6983124</v>
+        <v>6983189</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11150,7 +11155,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11160,7 +11165,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11171,6 +11176,11 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11187,10 +11197,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119899641</v>
+        <v>119898984</v>
       </c>
       <c r="B95" t="n">
-        <v>101097</v>
+        <v>94334</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11203,34 +11213,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670779</v>
+        <v>670792</v>
       </c>
       <c r="R95" t="n">
-        <v>6983125</v>
+        <v>6983157</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11262,7 +11272,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11272,7 +11282,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11299,10 +11309,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898495</v>
+        <v>119898758</v>
       </c>
       <c r="B96" t="n">
-        <v>57336</v>
+        <v>91879</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11311,51 +11321,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670817</v>
+        <v>670804</v>
       </c>
       <c r="R96" t="n">
-        <v>6983220</v>
+        <v>6983188</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11405,6 +11405,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11421,10 +11426,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898932</v>
+        <v>119895581</v>
       </c>
       <c r="B97" t="n">
-        <v>94346</v>
+        <v>91879</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11437,34 +11442,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2813</v>
+        <v>5964</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670806</v>
+        <v>670765</v>
       </c>
       <c r="R97" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11496,7 +11501,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11506,7 +11511,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11533,10 +11538,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119898913</v>
+        <v>119898741</v>
       </c>
       <c r="B98" t="n">
-        <v>57336</v>
+        <v>100103</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11545,25 +11550,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11573,10 +11578,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670820</v>
+        <v>670804</v>
       </c>
       <c r="R98" t="n">
-        <v>6983158</v>
+        <v>6983188</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11608,7 +11613,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11618,7 +11623,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11645,10 +11650,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119898758</v>
+        <v>119899641</v>
       </c>
       <c r="B99" t="n">
-        <v>91879</v>
+        <v>101097</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11661,34 +11666,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670804</v>
+        <v>670779</v>
       </c>
       <c r="R99" t="n">
-        <v>6983188</v>
+        <v>6983125</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11720,7 +11725,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11730,7 +11735,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11741,11 +11746,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898506</v>
+        <v>119899557</v>
       </c>
       <c r="B100" t="n">
-        <v>101097</v>
+        <v>91512</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11778,34 +11778,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670802</v>
+        <v>670765</v>
       </c>
       <c r="R100" t="n">
-        <v>6983219</v>
+        <v>6983124</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11858,11 +11858,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11879,10 +11874,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119898844</v>
+        <v>119898937</v>
       </c>
       <c r="B101" t="n">
-        <v>100194</v>
+        <v>94334</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11895,21 +11890,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11919,10 +11914,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670832</v>
+        <v>670806</v>
       </c>
       <c r="R101" t="n">
-        <v>6983190</v>
+        <v>6983157</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11954,7 +11949,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11964,7 +11959,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11991,7 +11986,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898741</v>
+        <v>119898663</v>
       </c>
       <c r="B102" t="n">
         <v>100103</v>
@@ -12031,10 +12026,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670804</v>
+        <v>670818</v>
       </c>
       <c r="R102" t="n">
-        <v>6983188</v>
+        <v>6983189</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12066,7 +12061,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12076,7 +12071,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12087,6 +12082,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12103,10 +12103,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119899557</v>
+        <v>119895594</v>
       </c>
       <c r="B103" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12119,34 +12119,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670765</v>
+        <v>670802</v>
       </c>
       <c r="R103" t="n">
-        <v>6983124</v>
+        <v>6983219</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12215,10 +12215,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898937</v>
+        <v>119898844</v>
       </c>
       <c r="B104" t="n">
-        <v>94334</v>
+        <v>100194</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12231,21 +12231,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12255,10 +12255,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670806</v>
+        <v>670832</v>
       </c>
       <c r="R104" t="n">
-        <v>6983157</v>
+        <v>6983190</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12327,10 +12327,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119898984</v>
+        <v>119898913</v>
       </c>
       <c r="B105" t="n">
-        <v>94334</v>
+        <v>57336</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12339,25 +12339,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670792</v>
+        <v>670820</v>
       </c>
       <c r="R105" t="n">
-        <v>6983157</v>
+        <v>6983158</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12439,10 +12439,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119900032</v>
+        <v>119898506</v>
       </c>
       <c r="B106" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12455,34 +12455,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670742</v>
+        <v>670802</v>
       </c>
       <c r="R106" t="n">
-        <v>6983030</v>
+        <v>6983219</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12535,6 +12535,11 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12551,10 +12556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119895581</v>
+        <v>119899251</v>
       </c>
       <c r="B107" t="n">
-        <v>91879</v>
+        <v>100103</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12567,34 +12572,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670765</v>
+        <v>670777</v>
       </c>
       <c r="R107" t="n">
-        <v>6983124</v>
+        <v>6983156</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12626,7 +12636,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12636,7 +12646,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12647,6 +12657,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12663,10 +12678,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119898663</v>
+        <v>119898932</v>
       </c>
       <c r="B108" t="n">
-        <v>100103</v>
+        <v>94346</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12679,21 +12694,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222771</v>
+        <v>2813</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12703,10 +12718,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670818</v>
+        <v>670806</v>
       </c>
       <c r="R108" t="n">
-        <v>6983189</v>
+        <v>6983157</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12738,7 +12753,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12748,7 +12763,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12759,11 +12774,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12780,10 +12790,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119899251</v>
+        <v>119899526</v>
       </c>
       <c r="B109" t="n">
-        <v>100103</v>
+        <v>105017</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12796,39 +12806,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222771</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670777</v>
+        <v>670765</v>
       </c>
       <c r="R109" t="n">
-        <v>6983156</v>
+        <v>6983124</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12860,7 +12865,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12870,7 +12875,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12881,11 +12886,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12902,7 +12902,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119895594</v>
+        <v>119900032</v>
       </c>
       <c r="B110" t="n">
         <v>100103</v>
@@ -12938,14 +12938,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670802</v>
+        <v>670742</v>
       </c>
       <c r="R110" t="n">
-        <v>6983219</v>
+        <v>6983030</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13014,10 +13014,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235197</v>
+        <v>120235122</v>
       </c>
       <c r="B111" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13030,21 +13030,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13116,10 +13116,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235111</v>
+        <v>120235198</v>
       </c>
       <c r="B112" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13132,21 +13132,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>670748</v>
+        <v>670732</v>
       </c>
       <c r="R112" t="n">
-        <v>6982992</v>
+        <v>6983014</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13218,7 +13218,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235119</v>
+        <v>120235118</v>
       </c>
       <c r="B113" t="n">
         <v>91512</v>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670847</v>
+        <v>670878</v>
       </c>
       <c r="R113" t="n">
-        <v>6983132</v>
+        <v>6983125</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235118</v>
+        <v>120235195</v>
       </c>
       <c r="B114" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670878</v>
+        <v>670813</v>
       </c>
       <c r="R114" t="n">
-        <v>6983125</v>
+        <v>6983126</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,10 +13422,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235194</v>
+        <v>120235121</v>
       </c>
       <c r="B115" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670904</v>
+        <v>670816</v>
       </c>
       <c r="R115" t="n">
-        <v>6983156</v>
+        <v>6983123</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235122</v>
+        <v>120235111</v>
       </c>
       <c r="B116" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13540,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670768</v>
+        <v>670748</v>
       </c>
       <c r="R116" t="n">
-        <v>6983085</v>
+        <v>6982992</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,7 +13626,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235198</v>
+        <v>120235194</v>
       </c>
       <c r="B117" t="n">
         <v>100194</v>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670732</v>
+        <v>670904</v>
       </c>
       <c r="R117" t="n">
-        <v>6983014</v>
+        <v>6983156</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13728,10 +13728,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235196</v>
+        <v>120235119</v>
       </c>
       <c r="B118" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13744,21 +13744,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670779</v>
+        <v>670847</v>
       </c>
       <c r="R118" t="n">
-        <v>6983095</v>
+        <v>6983132</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235121</v>
+        <v>120235196</v>
       </c>
       <c r="B119" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13846,21 +13846,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>670816</v>
+        <v>670779</v>
       </c>
       <c r="R119" t="n">
-        <v>6983123</v>
+        <v>6983095</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13932,7 +13932,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235195</v>
+        <v>120235197</v>
       </c>
       <c r="B120" t="n">
         <v>100194</v>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670813</v>
+        <v>670768</v>
       </c>
       <c r="R120" t="n">
-        <v>6983126</v>
+        <v>6983085</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -10841,10 +10841,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119898669</v>
+        <v>119898495</v>
       </c>
       <c r="B92" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10853,41 +10853,51 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670818</v>
+        <v>670817</v>
       </c>
       <c r="R92" t="n">
-        <v>6983189</v>
+        <v>6983220</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10916,7 +10926,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10926,7 +10936,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10937,11 +10947,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10958,10 +10963,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898495</v>
+        <v>119898669</v>
       </c>
       <c r="B93" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10970,51 +10975,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>670817</v>
+        <v>670818</v>
       </c>
       <c r="R93" t="n">
-        <v>6983220</v>
+        <v>6983189</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11043,7 +11038,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11053,7 +11048,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11064,6 +11059,11 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11080,7 +11080,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898656</v>
+        <v>119898506</v>
       </c>
       <c r="B94" t="n">
         <v>101097</v>
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670818</v>
+        <v>670802</v>
       </c>
       <c r="R94" t="n">
-        <v>6983189</v>
+        <v>6983219</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11197,10 +11197,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898984</v>
+        <v>119898663</v>
       </c>
       <c r="B95" t="n">
-        <v>94334</v>
+        <v>100103</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11213,21 +11213,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2809</v>
+        <v>222771</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11237,10 +11237,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670792</v>
+        <v>670818</v>
       </c>
       <c r="R95" t="n">
-        <v>6983157</v>
+        <v>6983189</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11293,6 +11293,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11309,10 +11314,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898758</v>
+        <v>119898932</v>
       </c>
       <c r="B96" t="n">
-        <v>91879</v>
+        <v>94346</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11325,21 +11330,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5964</v>
+        <v>2813</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11349,10 +11354,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670804</v>
+        <v>670806</v>
       </c>
       <c r="R96" t="n">
-        <v>6983188</v>
+        <v>6983157</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11384,7 +11389,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11394,7 +11399,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11405,11 +11410,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11426,10 +11426,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119895581</v>
+        <v>119898984</v>
       </c>
       <c r="B97" t="n">
-        <v>91879</v>
+        <v>94334</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11442,34 +11442,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5964</v>
+        <v>2809</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670765</v>
+        <v>670792</v>
       </c>
       <c r="R97" t="n">
-        <v>6983124</v>
+        <v>6983157</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11538,10 +11538,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119898741</v>
+        <v>119899526</v>
       </c>
       <c r="B98" t="n">
-        <v>100103</v>
+        <v>105017</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11554,34 +11554,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>221725</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670804</v>
+        <v>670765</v>
       </c>
       <c r="R98" t="n">
-        <v>6983188</v>
+        <v>6983124</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11650,10 +11650,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119899641</v>
+        <v>119898844</v>
       </c>
       <c r="B99" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11666,34 +11666,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670779</v>
+        <v>670832</v>
       </c>
       <c r="R99" t="n">
-        <v>6983125</v>
+        <v>6983190</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119899557</v>
+        <v>119898741</v>
       </c>
       <c r="B100" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11778,34 +11778,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R100" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11986,10 +11986,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898663</v>
+        <v>119898656</v>
       </c>
       <c r="B102" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12002,21 +12002,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12103,10 +12103,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119895594</v>
+        <v>119899557</v>
       </c>
       <c r="B103" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12119,34 +12119,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670802</v>
+        <v>670765</v>
       </c>
       <c r="R103" t="n">
-        <v>6983219</v>
+        <v>6983124</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12215,10 +12215,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119898844</v>
+        <v>119899251</v>
       </c>
       <c r="B104" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12231,34 +12231,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670832</v>
+        <v>670777</v>
       </c>
       <c r="R104" t="n">
-        <v>6983190</v>
+        <v>6983156</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12290,7 +12295,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12300,7 +12305,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12311,6 +12316,11 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12327,10 +12337,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119898913</v>
+        <v>119900032</v>
       </c>
       <c r="B105" t="n">
-        <v>57336</v>
+        <v>100103</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12339,38 +12349,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670820</v>
+        <v>670742</v>
       </c>
       <c r="R105" t="n">
-        <v>6983158</v>
+        <v>6983030</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12402,7 +12412,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12412,7 +12422,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12439,7 +12449,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119898506</v>
+        <v>119899641</v>
       </c>
       <c r="B106" t="n">
         <v>101097</v>
@@ -12475,14 +12485,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670802</v>
+        <v>670779</v>
       </c>
       <c r="R106" t="n">
-        <v>6983219</v>
+        <v>6983125</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12514,7 +12524,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12524,7 +12534,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12535,11 +12545,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12556,10 +12561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119899251</v>
+        <v>119898913</v>
       </c>
       <c r="B107" t="n">
-        <v>100103</v>
+        <v>57336</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12568,43 +12573,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670777</v>
+        <v>670820</v>
       </c>
       <c r="R107" t="n">
-        <v>6983156</v>
+        <v>6983158</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12657,11 +12657,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12678,10 +12673,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119898932</v>
+        <v>119895594</v>
       </c>
       <c r="B108" t="n">
-        <v>94346</v>
+        <v>100103</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12694,21 +12689,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2813</v>
+        <v>222771</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12718,10 +12713,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670806</v>
+        <v>670802</v>
       </c>
       <c r="R108" t="n">
-        <v>6983157</v>
+        <v>6983219</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12753,7 +12748,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12763,7 +12758,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12790,10 +12785,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119899526</v>
+        <v>119898758</v>
       </c>
       <c r="B109" t="n">
-        <v>105017</v>
+        <v>91879</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12806,34 +12801,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>5964</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R109" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12865,7 +12860,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12875,7 +12870,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12886,6 +12881,11 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12902,10 +12902,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119900032</v>
+        <v>119895581</v>
       </c>
       <c r="B110" t="n">
-        <v>100103</v>
+        <v>91879</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12918,34 +12918,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670742</v>
+        <v>670765</v>
       </c>
       <c r="R110" t="n">
-        <v>6983030</v>
+        <v>6983124</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13014,10 +13014,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235122</v>
+        <v>120235118</v>
       </c>
       <c r="B111" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13030,21 +13030,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670768</v>
+        <v>670878</v>
       </c>
       <c r="R111" t="n">
-        <v>6983085</v>
+        <v>6983125</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235198</v>
+        <v>120235197</v>
       </c>
       <c r="B112" t="n">
         <v>100194</v>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>670732</v>
+        <v>670768</v>
       </c>
       <c r="R112" t="n">
-        <v>6983014</v>
+        <v>6983085</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13218,10 +13218,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235118</v>
+        <v>120235111</v>
       </c>
       <c r="B113" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13234,21 +13234,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670878</v>
+        <v>670748</v>
       </c>
       <c r="R113" t="n">
-        <v>6983125</v>
+        <v>6982992</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235195</v>
+        <v>120235194</v>
       </c>
       <c r="B114" t="n">
         <v>100194</v>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670813</v>
+        <v>670904</v>
       </c>
       <c r="R114" t="n">
-        <v>6983126</v>
+        <v>6983156</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,10 +13422,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235121</v>
+        <v>120235198</v>
       </c>
       <c r="B115" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670816</v>
+        <v>670732</v>
       </c>
       <c r="R115" t="n">
-        <v>6983123</v>
+        <v>6983014</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235111</v>
+        <v>120235122</v>
       </c>
       <c r="B116" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13540,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670748</v>
+        <v>670768</v>
       </c>
       <c r="R116" t="n">
-        <v>6982992</v>
+        <v>6983085</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,7 +13626,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235194</v>
+        <v>120235196</v>
       </c>
       <c r="B117" t="n">
         <v>100194</v>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670904</v>
+        <v>670779</v>
       </c>
       <c r="R117" t="n">
-        <v>6983156</v>
+        <v>6983095</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13728,10 +13728,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235119</v>
+        <v>120235195</v>
       </c>
       <c r="B118" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13744,21 +13744,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670847</v>
+        <v>670813</v>
       </c>
       <c r="R118" t="n">
-        <v>6983132</v>
+        <v>6983126</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235196</v>
+        <v>120235121</v>
       </c>
       <c r="B119" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13846,21 +13846,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>670779</v>
+        <v>670816</v>
       </c>
       <c r="R119" t="n">
-        <v>6983095</v>
+        <v>6983123</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13932,10 +13932,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235197</v>
+        <v>120235119</v>
       </c>
       <c r="B120" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13948,21 +13948,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670768</v>
+        <v>670847</v>
       </c>
       <c r="R120" t="n">
-        <v>6983085</v>
+        <v>6983132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -12673,10 +12673,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119895594</v>
+        <v>119898758</v>
       </c>
       <c r="B108" t="n">
-        <v>100103</v>
+        <v>91879</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12689,21 +12689,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12713,10 +12713,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670802</v>
+        <v>670804</v>
       </c>
       <c r="R108" t="n">
-        <v>6983219</v>
+        <v>6983188</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12769,6 +12769,11 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12785,10 +12790,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119898758</v>
+        <v>119895594</v>
       </c>
       <c r="B109" t="n">
-        <v>91879</v>
+        <v>100103</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12801,21 +12806,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12825,10 +12830,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670804</v>
+        <v>670802</v>
       </c>
       <c r="R109" t="n">
-        <v>6983188</v>
+        <v>6983219</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12860,7 +12865,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12870,7 +12875,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12881,11 +12886,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -13014,10 +13014,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235118</v>
+        <v>120235196</v>
       </c>
       <c r="B111" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13030,21 +13030,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670878</v>
+        <v>670779</v>
       </c>
       <c r="R111" t="n">
-        <v>6983125</v>
+        <v>6983095</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13116,10 +13116,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235197</v>
+        <v>120235122</v>
       </c>
       <c r="B112" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13132,21 +13132,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13218,10 +13218,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235111</v>
+        <v>120235198</v>
       </c>
       <c r="B113" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13234,21 +13234,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670748</v>
+        <v>670732</v>
       </c>
       <c r="R113" t="n">
-        <v>6982992</v>
+        <v>6983014</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235194</v>
+        <v>120235121</v>
       </c>
       <c r="B114" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670904</v>
+        <v>670816</v>
       </c>
       <c r="R114" t="n">
-        <v>6983156</v>
+        <v>6983123</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,10 +13422,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235198</v>
+        <v>120235111</v>
       </c>
       <c r="B115" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670732</v>
+        <v>670748</v>
       </c>
       <c r="R115" t="n">
-        <v>6983014</v>
+        <v>6982992</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235122</v>
+        <v>120235118</v>
       </c>
       <c r="B116" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13540,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670768</v>
+        <v>670878</v>
       </c>
       <c r="R116" t="n">
-        <v>6983085</v>
+        <v>6983125</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,7 +13626,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235196</v>
+        <v>120235195</v>
       </c>
       <c r="B117" t="n">
         <v>100194</v>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670779</v>
+        <v>670813</v>
       </c>
       <c r="R117" t="n">
-        <v>6983095</v>
+        <v>6983126</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13728,7 +13728,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235195</v>
+        <v>120235197</v>
       </c>
       <c r="B118" t="n">
         <v>100194</v>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670813</v>
+        <v>670768</v>
       </c>
       <c r="R118" t="n">
-        <v>6983126</v>
+        <v>6983085</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235121</v>
+        <v>120235119</v>
       </c>
       <c r="B119" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13846,21 +13846,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>670816</v>
+        <v>670847</v>
       </c>
       <c r="R119" t="n">
-        <v>6983123</v>
+        <v>6983132</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13932,10 +13932,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235119</v>
+        <v>120235194</v>
       </c>
       <c r="B120" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13948,21 +13948,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670847</v>
+        <v>670904</v>
       </c>
       <c r="R120" t="n">
-        <v>6983132</v>
+        <v>6983156</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -13014,7 +13014,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235196</v>
+        <v>120235195</v>
       </c>
       <c r="B111" t="n">
         <v>100194</v>
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670779</v>
+        <v>670813</v>
       </c>
       <c r="R111" t="n">
-        <v>6983095</v>
+        <v>6983126</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13116,10 +13116,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235122</v>
+        <v>120235196</v>
       </c>
       <c r="B112" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13132,21 +13132,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>670768</v>
+        <v>670779</v>
       </c>
       <c r="R112" t="n">
-        <v>6983085</v>
+        <v>6983095</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13218,7 +13218,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235198</v>
+        <v>120235197</v>
       </c>
       <c r="B113" t="n">
         <v>100194</v>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>670732</v>
+        <v>670768</v>
       </c>
       <c r="R113" t="n">
-        <v>6983014</v>
+        <v>6983085</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235121</v>
+        <v>120235118</v>
       </c>
       <c r="B114" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670816</v>
+        <v>670878</v>
       </c>
       <c r="R114" t="n">
-        <v>6983123</v>
+        <v>6983125</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,10 +13422,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235111</v>
+        <v>120235198</v>
       </c>
       <c r="B115" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13438,21 +13438,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670748</v>
+        <v>670732</v>
       </c>
       <c r="R115" t="n">
-        <v>6982992</v>
+        <v>6983014</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235118</v>
+        <v>120235121</v>
       </c>
       <c r="B116" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13540,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670878</v>
+        <v>670816</v>
       </c>
       <c r="R116" t="n">
-        <v>6983125</v>
+        <v>6983123</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,10 +13626,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235195</v>
+        <v>120235111</v>
       </c>
       <c r="B117" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13642,21 +13642,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670813</v>
+        <v>670748</v>
       </c>
       <c r="R117" t="n">
-        <v>6983126</v>
+        <v>6982992</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13728,7 +13728,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120235197</v>
+        <v>120235194</v>
       </c>
       <c r="B118" t="n">
         <v>100194</v>
@@ -13768,10 +13768,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>670768</v>
+        <v>670904</v>
       </c>
       <c r="R118" t="n">
-        <v>6983085</v>
+        <v>6983156</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13830,10 +13830,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120235119</v>
+        <v>120235122</v>
       </c>
       <c r="B119" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13846,21 +13846,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>670847</v>
+        <v>670768</v>
       </c>
       <c r="R119" t="n">
-        <v>6983132</v>
+        <v>6983085</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13932,10 +13932,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120235194</v>
+        <v>120235119</v>
       </c>
       <c r="B120" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13948,21 +13948,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>670904</v>
+        <v>670847</v>
       </c>
       <c r="R120" t="n">
-        <v>6983156</v>
+        <v>6983132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -14037,7 +14037,7 @@
         <v>121087115</v>
       </c>
       <c r="B121" t="n">
-        <v>83072</v>
+        <v>83075</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -14037,7 +14037,7 @@
         <v>121087115</v>
       </c>
       <c r="B121" t="n">
-        <v>83075</v>
+        <v>83080</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3255,10 +3255,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111631355</v>
+        <v>112362927</v>
       </c>
       <c r="B24" t="n">
-        <v>98535</v>
+        <v>90910</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3271,35 +3271,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>670741</v>
+        <v>670889</v>
       </c>
       <c r="R24" t="n">
-        <v>6983061</v>
+        <v>6983193</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3352,6 +3352,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3368,10 +3373,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111631806</v>
+        <v>112362904</v>
       </c>
       <c r="B25" t="n">
-        <v>98535</v>
+        <v>85498</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3384,21 +3389,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1988</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3409,10 +3414,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>670778</v>
+        <v>670874</v>
       </c>
       <c r="R25" t="n">
-        <v>6983156</v>
+        <v>6983192</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3439,22 +3444,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112362927</v>
+        <v>112362935</v>
       </c>
       <c r="B26" t="n">
-        <v>90910</v>
+        <v>99097</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3502,21 +3507,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4363</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3527,10 +3532,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>670889</v>
+        <v>670874</v>
       </c>
       <c r="R26" t="n">
-        <v>6983193</v>
+        <v>6983192</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3562,7 +3567,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3572,7 +3577,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,10 +3609,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112362904</v>
+        <v>112362960</v>
       </c>
       <c r="B27" t="n">
-        <v>85498</v>
+        <v>90926</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3620,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1988</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,7 +3685,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3690,7 +3695,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,10 +3727,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112362935</v>
+        <v>112362911</v>
       </c>
       <c r="B28" t="n">
-        <v>99097</v>
+        <v>85443</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3738,21 +3743,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>3624</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3798,7 +3803,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3808,7 +3813,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3840,10 +3845,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112362960</v>
+        <v>112362953</v>
       </c>
       <c r="B29" t="n">
-        <v>90926</v>
+        <v>91626</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3856,32 +3861,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>670874</v>
+        <v>670875</v>
       </c>
       <c r="R29" t="n">
         <v>6983192</v>
@@ -3929,18 +3936,29 @@
           <t>10:40</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ingen tall i direkt nära avstånd, fruktkroppar typiska. Mycket spridd och riklig på berget.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkgranskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3958,10 +3976,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112362911</v>
+        <v>112507267</v>
       </c>
       <c r="B30" t="n">
-        <v>85443</v>
+        <v>85548</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3970,25 +3988,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3624</v>
+        <v>3739</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3999,10 +4017,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>670874</v>
+        <v>670889</v>
       </c>
       <c r="R30" t="n">
-        <v>6983192</v>
+        <v>6983193</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4034,7 +4052,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4044,7 +4062,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Typisk doft, men ska efterhandsmikroskoperas för jämförelse med elegantior (som dock i stort sett saknas i norra Sverige och ej är funnen i ång).</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4058,7 +4081,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4076,10 +4099,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112362953</v>
+        <v>112918582</v>
       </c>
       <c r="B31" t="n">
-        <v>91626</v>
+        <v>99339</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4092,37 +4115,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>670875</v>
+        <v>670744</v>
       </c>
       <c r="R31" t="n">
-        <v>6983192</v>
+        <v>6982999</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4149,27 +4170,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ingen tall i direkt nära avstånd, fruktkroppar typiska. Mycket spridd och riklig på berget.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4178,19 +4194,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4207,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112507267</v>
+        <v>113778170</v>
       </c>
       <c r="B32" t="n">
-        <v>85548</v>
+        <v>100812</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4219,39 +4224,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3739</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>670889</v>
+        <v>670729</v>
       </c>
       <c r="R32" t="n">
-        <v>6983193</v>
+        <v>6982998</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4278,27 +4283,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Typisk doft, men ska efterhandsmikroskoperas för jämförelse med elegantior (som dock i stort sett saknas i norra Sverige och ej är funnen i ång).</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112918582</v>
+        <v>117495741</v>
       </c>
       <c r="B33" t="n">
-        <v>99339</v>
+        <v>100009</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4364,17 +4364,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten N, Nordingrå (Middagsklinten N, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>670744</v>
+        <v>670806</v>
       </c>
       <c r="R33" t="n">
-        <v>6982999</v>
+        <v>6983157</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4401,22 +4405,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4427,6 +4431,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4443,10 +4452,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113778170</v>
+        <v>117496085</v>
       </c>
       <c r="B34" t="n">
-        <v>100812</v>
+        <v>101002</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4477,17 +4486,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten N (Middagsklinten N, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>670729</v>
+        <v>670793</v>
       </c>
       <c r="R34" t="n">
-        <v>6982998</v>
+        <v>6983126</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4514,22 +4527,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4540,11 +4553,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4561,10 +4569,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117495741</v>
+        <v>117495636</v>
       </c>
       <c r="B35" t="n">
-        <v>100009</v>
+        <v>100099</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4577,36 +4585,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå (Middagsklinten N, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>670806</v>
+        <v>670792</v>
       </c>
       <c r="R35" t="n">
         <v>6983157</v>
@@ -4641,7 +4644,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4651,7 +4654,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4683,10 +4686,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117496085</v>
+        <v>117495994</v>
       </c>
       <c r="B36" t="n">
-        <v>101002</v>
+        <v>100099</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4699,39 +4702,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Middagsklinten N (Middagsklinten N, Nordingrå), Ång</t>
+          <t>Middagsklinten N, Nordingrå (Middagsklinten N, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>670793</v>
+        <v>670806</v>
       </c>
       <c r="R36" t="n">
-        <v>6983126</v>
+        <v>6983157</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4763,7 +4761,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4773,7 +4771,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4800,7 +4798,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117495636</v>
+        <v>117495789</v>
       </c>
       <c r="B37" t="n">
         <v>100099</v>
@@ -4840,10 +4838,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>670792</v>
+        <v>670804</v>
       </c>
       <c r="R37" t="n">
-        <v>6983157</v>
+        <v>6983188</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4875,7 +4873,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4885,7 +4883,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4896,11 +4894,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4917,7 +4910,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117495994</v>
+        <v>117495258</v>
       </c>
       <c r="B38" t="n">
         <v>100099</v>
@@ -4957,10 +4950,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>670806</v>
+        <v>670790</v>
       </c>
       <c r="R38" t="n">
-        <v>6983157</v>
+        <v>6983188</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4992,7 +4985,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5002,7 +4995,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5029,10 +5022,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117495789</v>
+        <v>117520374</v>
       </c>
       <c r="B39" t="n">
-        <v>100099</v>
+        <v>101002</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5045,34 +5038,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå (Middagsklinten N, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>670804</v>
+        <v>670777</v>
       </c>
       <c r="R39" t="n">
-        <v>6983188</v>
+        <v>6983156</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5104,7 +5102,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5114,7 +5112,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5125,6 +5123,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5141,10 +5144,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117495258</v>
+        <v>117521249</v>
       </c>
       <c r="B40" t="n">
-        <v>100099</v>
+        <v>101002</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,34 +5160,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå (Middagsklinten N, Nordingrå), Ång</t>
+          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>670790</v>
+        <v>670752</v>
       </c>
       <c r="R40" t="n">
-        <v>6983188</v>
+        <v>6983093</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5216,7 +5219,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5226,7 +5229,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5253,7 +5256,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117520374</v>
+        <v>117521233</v>
       </c>
       <c r="B41" t="n">
         <v>101002</v>
@@ -5294,14 +5297,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå (Middagsklinten N, Nordingrå), Ång</t>
+          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>670777</v>
+        <v>670767</v>
       </c>
       <c r="R41" t="n">
-        <v>6983156</v>
+        <v>6983093</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5333,7 +5336,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5343,7 +5346,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5354,11 +5357,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5375,10 +5373,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117521249</v>
+        <v>117522210</v>
       </c>
       <c r="B42" t="n">
-        <v>101002</v>
+        <v>100009</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5391,21 +5389,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5415,10 +5413,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>670752</v>
+        <v>670740</v>
       </c>
       <c r="R42" t="n">
-        <v>6983093</v>
+        <v>6983061</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5450,7 +5448,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5460,7 +5458,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5487,10 +5485,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117521233</v>
+        <v>117522393</v>
       </c>
       <c r="B43" t="n">
-        <v>101002</v>
+        <v>100009</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5503,39 +5501,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>670767</v>
+        <v>670739</v>
       </c>
       <c r="R43" t="n">
-        <v>6983093</v>
+        <v>6982976</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5567,7 +5560,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5577,7 +5570,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5604,7 +5597,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117522210</v>
+        <v>117522336</v>
       </c>
       <c r="B44" t="n">
         <v>100009</v>
@@ -5638,19 +5631,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>670740</v>
+        <v>670771</v>
       </c>
       <c r="R44" t="n">
-        <v>6983061</v>
+        <v>6983001</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5679,7 +5677,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5689,7 +5687,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5716,10 +5714,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117522393</v>
+        <v>117521257</v>
       </c>
       <c r="B45" t="n">
-        <v>100009</v>
+        <v>100099</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5732,34 +5730,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>670739</v>
+        <v>670752</v>
       </c>
       <c r="R45" t="n">
-        <v>6982976</v>
+        <v>6983093</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5791,7 +5789,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5801,7 +5799,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5828,10 +5826,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117522336</v>
+        <v>117522356</v>
       </c>
       <c r="B46" t="n">
-        <v>100009</v>
+        <v>100099</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5844,29 +5842,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
@@ -5945,10 +5938,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117521257</v>
+        <v>117522160</v>
       </c>
       <c r="B47" t="n">
-        <v>100099</v>
+        <v>100009</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5961,24 +5954,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
@@ -6020,7 +6018,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6030,7 +6028,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6041,6 +6039,11 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6057,7 +6060,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117522356</v>
+        <v>117522070</v>
       </c>
       <c r="B48" t="n">
         <v>100099</v>
@@ -6097,13 +6100,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>670771</v>
+        <v>670767</v>
       </c>
       <c r="R48" t="n">
-        <v>6983001</v>
+        <v>6983093</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6132,7 +6135,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6142,7 +6145,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6153,6 +6156,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6169,10 +6177,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117522160</v>
+        <v>117522413</v>
       </c>
       <c r="B49" t="n">
-        <v>100009</v>
+        <v>101002</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6185,39 +6193,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Middagsklinten, Nordingrå (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten (Middagsklinten, Nordingrå ), Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>670752</v>
+        <v>670744</v>
       </c>
       <c r="R49" t="n">
-        <v>6983093</v>
+        <v>6982999</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6249,7 +6257,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6259,7 +6267,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6270,11 +6278,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6291,10 +6294,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117522070</v>
+        <v>119781377</v>
       </c>
       <c r="B50" t="n">
-        <v>100099</v>
+        <v>57336</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6303,41 +6306,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Middagsklinten (Middagsklinten, Nordingrå), Ång</t>
+          <t>Middagsklinten+Stormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>670767</v>
+        <v>670794</v>
       </c>
       <c r="R50" t="n">
-        <v>6983093</v>
+        <v>6983144</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,22 +6364,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6387,31 +6380,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117522413</v>
+        <v>119781369</v>
       </c>
       <c r="B51" t="n">
-        <v>101002</v>
+        <v>91512</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6424,42 +6412,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Middagsklinten (Middagsklinten, Nordingrå ), Ång</t>
+          <t>Middagsklinten+Stormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>670744</v>
+        <v>670819</v>
       </c>
       <c r="R51" t="n">
-        <v>6982999</v>
+        <v>6983261</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6483,22 +6466,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6513,22 +6486,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119781377</v>
+        <v>119781469</v>
       </c>
       <c r="B52" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,25 +6510,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6565,10 +6538,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>670794</v>
+        <v>670788</v>
       </c>
       <c r="R52" t="n">
-        <v>6983144</v>
+        <v>6983134</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,10 +6600,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119781369</v>
+        <v>119781350</v>
       </c>
       <c r="B53" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6643,21 +6616,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6667,10 +6640,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>670819</v>
+        <v>670791</v>
       </c>
       <c r="R53" t="n">
-        <v>6983261</v>
+        <v>6983132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6729,10 +6702,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119781469</v>
+        <v>119781392</v>
       </c>
       <c r="B54" t="n">
-        <v>100194</v>
+        <v>91868</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6741,25 +6714,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>789</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6769,10 +6742,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>670788</v>
+        <v>670901</v>
       </c>
       <c r="R54" t="n">
-        <v>6983134</v>
+        <v>6983185</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6831,10 +6804,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119781350</v>
+        <v>119781438</v>
       </c>
       <c r="B55" t="n">
-        <v>101097</v>
+        <v>91879</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6847,21 +6820,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6871,10 +6844,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>670791</v>
+        <v>670906</v>
       </c>
       <c r="R55" t="n">
-        <v>6983132</v>
+        <v>6983256</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6933,10 +6906,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119781392</v>
+        <v>119781352</v>
       </c>
       <c r="B56" t="n">
-        <v>91868</v>
+        <v>101097</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6945,25 +6918,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>789</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6973,10 +6946,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>670901</v>
+        <v>670782</v>
       </c>
       <c r="R56" t="n">
-        <v>6983185</v>
+        <v>6983174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7035,10 +7008,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119781438</v>
+        <v>119781470</v>
       </c>
       <c r="B57" t="n">
-        <v>91879</v>
+        <v>100194</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7051,21 +7024,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7075,10 +7048,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>670906</v>
+        <v>670778</v>
       </c>
       <c r="R57" t="n">
-        <v>6983256</v>
+        <v>6983109</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7137,10 +7110,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119781352</v>
+        <v>119781447</v>
       </c>
       <c r="B58" t="n">
-        <v>101097</v>
+        <v>91876</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7149,25 +7122,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7177,10 +7150,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>670782</v>
+        <v>670905</v>
       </c>
       <c r="R58" t="n">
-        <v>6983174</v>
+        <v>6983220</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7239,10 +7212,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119781470</v>
+        <v>119781385</v>
       </c>
       <c r="B59" t="n">
-        <v>100194</v>
+        <v>89256</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7255,21 +7228,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6268</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7279,10 +7252,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>670778</v>
+        <v>670900</v>
       </c>
       <c r="R59" t="n">
-        <v>6983109</v>
+        <v>6983212</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7341,10 +7314,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119781447</v>
+        <v>119781348</v>
       </c>
       <c r="B60" t="n">
-        <v>91876</v>
+        <v>101097</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7353,25 +7326,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4368</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7381,10 +7354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670905</v>
+        <v>670779</v>
       </c>
       <c r="R60" t="n">
-        <v>6983220</v>
+        <v>6983126</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7443,10 +7416,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119781385</v>
+        <v>119781414</v>
       </c>
       <c r="B61" t="n">
-        <v>89256</v>
+        <v>86305</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7455,25 +7428,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6268</v>
+        <v>426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7483,10 +7456,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670900</v>
+        <v>670832</v>
       </c>
       <c r="R61" t="n">
-        <v>6983212</v>
+        <v>6983235</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,10 +7518,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119781348</v>
+        <v>119781440</v>
       </c>
       <c r="B62" t="n">
-        <v>101097</v>
+        <v>91879</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7561,21 +7534,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7585,10 +7558,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>670779</v>
+        <v>670899</v>
       </c>
       <c r="R62" t="n">
-        <v>6983126</v>
+        <v>6983187</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7647,10 +7620,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119781414</v>
+        <v>119781439</v>
       </c>
       <c r="B63" t="n">
-        <v>86305</v>
+        <v>91879</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7659,25 +7632,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>426</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7687,10 +7660,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>670832</v>
+        <v>670893</v>
       </c>
       <c r="R63" t="n">
-        <v>6983235</v>
+        <v>6983206</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7749,10 +7722,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119781440</v>
+        <v>119781449</v>
       </c>
       <c r="B64" t="n">
-        <v>91879</v>
+        <v>91876</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7761,25 +7734,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7789,10 +7762,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>670899</v>
+        <v>670901</v>
       </c>
       <c r="R64" t="n">
-        <v>6983187</v>
+        <v>6983219</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7851,10 +7824,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119781439</v>
+        <v>119781368</v>
       </c>
       <c r="B65" t="n">
-        <v>91879</v>
+        <v>91512</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7867,21 +7840,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7891,10 +7864,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670893</v>
+        <v>670847</v>
       </c>
       <c r="R65" t="n">
-        <v>6983206</v>
+        <v>6983303</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7953,10 +7926,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119781449</v>
+        <v>119781359</v>
       </c>
       <c r="B66" t="n">
-        <v>91876</v>
+        <v>100103</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7965,25 +7938,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>222771</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7993,10 +7966,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>670901</v>
+        <v>670836</v>
       </c>
       <c r="R66" t="n">
-        <v>6983219</v>
+        <v>6983189</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8055,10 +8028,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119781368</v>
+        <v>119781353</v>
       </c>
       <c r="B67" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8071,21 +8044,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8095,10 +8068,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>670847</v>
+        <v>670761</v>
       </c>
       <c r="R67" t="n">
-        <v>6983303</v>
+        <v>6983130</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8157,10 +8130,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119781359</v>
+        <v>119781361</v>
       </c>
       <c r="B68" t="n">
-        <v>100103</v>
+        <v>105019</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8173,21 +8146,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>224098</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8197,10 +8170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670836</v>
+        <v>670789</v>
       </c>
       <c r="R68" t="n">
-        <v>6983189</v>
+        <v>6983134</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8241,6 +8214,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8259,10 +8233,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119781353</v>
+        <v>119781370</v>
       </c>
       <c r="B69" t="n">
-        <v>101097</v>
+        <v>91512</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8275,21 +8249,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8299,10 +8273,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>670761</v>
+        <v>670776</v>
       </c>
       <c r="R69" t="n">
-        <v>6983130</v>
+        <v>6983129</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8361,10 +8335,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119781361</v>
+        <v>119781448</v>
       </c>
       <c r="B70" t="n">
-        <v>105019</v>
+        <v>91876</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8373,25 +8347,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>224098</v>
+        <v>4368</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8401,10 +8375,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>670789</v>
+        <v>670902</v>
       </c>
       <c r="R70" t="n">
-        <v>6983134</v>
+        <v>6983235</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8445,7 +8419,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8464,10 +8437,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119781370</v>
+        <v>119781410</v>
       </c>
       <c r="B71" t="n">
-        <v>91512</v>
+        <v>91866</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8476,25 +8449,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4769</v>
+        <v>2058</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8504,10 +8477,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>670776</v>
+        <v>670897</v>
       </c>
       <c r="R71" t="n">
-        <v>6983129</v>
+        <v>6983186</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8566,10 +8539,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119781448</v>
+        <v>119789631</v>
       </c>
       <c r="B72" t="n">
-        <v>91876</v>
+        <v>100194</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8578,41 +8551,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Middagsklinten+Stormyrberget, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>670902</v>
+        <v>670906</v>
       </c>
       <c r="R72" t="n">
-        <v>6983235</v>
+        <v>6983132</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8639,9 +8612,19 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8656,22 +8639,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119781410</v>
+        <v>119789861</v>
       </c>
       <c r="B73" t="n">
-        <v>91866</v>
+        <v>100194</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8680,41 +8663,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2058</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Middagsklinten+Stormyrberget, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>670897</v>
+        <v>670873</v>
       </c>
       <c r="R73" t="n">
-        <v>6983186</v>
+        <v>6983173</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8741,9 +8724,19 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8758,22 +8751,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119789631</v>
+        <v>119789841</v>
       </c>
       <c r="B74" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8786,21 +8779,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8810,10 +8803,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>670906</v>
+        <v>670817</v>
       </c>
       <c r="R74" t="n">
-        <v>6983132</v>
+        <v>6983220</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8845,7 +8838,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8855,7 +8848,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8882,7 +8875,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119789861</v>
+        <v>119788949</v>
       </c>
       <c r="B75" t="n">
         <v>100194</v>
@@ -8922,10 +8915,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>670873</v>
+        <v>670878</v>
       </c>
       <c r="R75" t="n">
-        <v>6983173</v>
+        <v>6983130</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8957,7 +8950,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8967,7 +8960,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8994,7 +8987,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119789841</v>
+        <v>119789381</v>
       </c>
       <c r="B76" t="n">
         <v>100103</v>
@@ -9034,10 +9027,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>670817</v>
+        <v>670878</v>
       </c>
       <c r="R76" t="n">
-        <v>6983220</v>
+        <v>6983130</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9069,7 +9062,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9079,7 +9072,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9106,7 +9099,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788949</v>
+        <v>119788502</v>
       </c>
       <c r="B77" t="n">
         <v>100194</v>
@@ -9142,14 +9135,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>670878</v>
+        <v>670807</v>
       </c>
       <c r="R77" t="n">
-        <v>6983130</v>
+        <v>6983126</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9181,7 +9174,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9191,7 +9184,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9218,10 +9211,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119789381</v>
+        <v>119788561</v>
       </c>
       <c r="B78" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9234,21 +9227,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9258,10 +9251,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>670878</v>
+        <v>670806</v>
       </c>
       <c r="R78" t="n">
-        <v>6983130</v>
+        <v>6983157</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9293,7 +9286,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9303,7 +9296,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9314,6 +9307,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9330,10 +9328,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788502</v>
+        <v>119788402</v>
       </c>
       <c r="B79" t="n">
-        <v>100194</v>
+        <v>91876</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9342,38 +9340,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670807</v>
+        <v>670846</v>
       </c>
       <c r="R79" t="n">
-        <v>6983126</v>
+        <v>6983191</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9405,7 +9403,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9415,7 +9413,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9426,6 +9429,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9442,10 +9450,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788561</v>
+        <v>119789925</v>
       </c>
       <c r="B80" t="n">
-        <v>101097</v>
+        <v>94334</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9458,34 +9466,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>670806</v>
+        <v>670884</v>
       </c>
       <c r="R80" t="n">
-        <v>6983157</v>
+        <v>6983286</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9517,7 +9525,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9527,7 +9535,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9538,11 +9546,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9559,10 +9562,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119788402</v>
+        <v>119804619</v>
       </c>
       <c r="B81" t="n">
-        <v>91876</v>
+        <v>100194</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9571,25 +9574,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4368</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9599,10 +9602,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>670846</v>
+        <v>670802</v>
       </c>
       <c r="R81" t="n">
-        <v>6983191</v>
+        <v>6983219</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9634,7 +9637,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9644,12 +9647,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Klassisk doft, fruktkropparna på bild något åldrade och mörka.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9660,11 +9658,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9681,10 +9674,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119789925</v>
+        <v>119789399</v>
       </c>
       <c r="B82" t="n">
-        <v>94334</v>
+        <v>91512</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9697,34 +9690,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670884</v>
+        <v>670892</v>
       </c>
       <c r="R82" t="n">
-        <v>6983286</v>
+        <v>6983131</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9756,7 +9749,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9766,7 +9759,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9793,7 +9786,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119804619</v>
+        <v>119789352</v>
       </c>
       <c r="B83" t="n">
         <v>100194</v>
@@ -9833,10 +9826,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>670802</v>
+        <v>670892</v>
       </c>
       <c r="R83" t="n">
-        <v>6983219</v>
+        <v>6983131</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9868,7 +9861,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9878,7 +9871,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9889,6 +9882,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9905,10 +9903,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119789399</v>
+        <v>119789062</v>
       </c>
       <c r="B84" t="n">
-        <v>91512</v>
+        <v>100194</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9921,21 +9919,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9945,10 +9943,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>670892</v>
+        <v>670848</v>
       </c>
       <c r="R84" t="n">
-        <v>6983131</v>
+        <v>6983160</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9980,7 +9978,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9990,7 +9988,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10001,6 +9999,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10017,10 +10020,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119789352</v>
+        <v>119788516</v>
       </c>
       <c r="B85" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10029,38 +10032,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>670892</v>
+        <v>670807</v>
       </c>
       <c r="R85" t="n">
-        <v>6983131</v>
+        <v>6983126</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10092,7 +10100,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10102,7 +10110,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10134,10 +10142,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119789062</v>
+        <v>119788716</v>
       </c>
       <c r="B86" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10150,34 +10158,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>670848</v>
+        <v>670864</v>
       </c>
       <c r="R86" t="n">
-        <v>6983160</v>
+        <v>6983129</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10209,7 +10217,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10219,7 +10227,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10251,10 +10259,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788516</v>
+        <v>119804612</v>
       </c>
       <c r="B87" t="n">
-        <v>57336</v>
+        <v>94334</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10263,43 +10271,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>670807</v>
+        <v>670802</v>
       </c>
       <c r="R87" t="n">
-        <v>6983126</v>
+        <v>6983219</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10331,7 +10334,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10341,7 +10344,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10352,11 +10355,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10373,10 +10371,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788716</v>
+        <v>119788496</v>
       </c>
       <c r="B88" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10389,21 +10387,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10413,10 +10411,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>670864</v>
+        <v>670807</v>
       </c>
       <c r="R88" t="n">
-        <v>6983129</v>
+        <v>6983126</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10448,7 +10446,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10458,7 +10456,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10490,10 +10488,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119804612</v>
+        <v>119842147</v>
       </c>
       <c r="B89" t="n">
-        <v>94334</v>
+        <v>105019</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10506,34 +10504,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>224098</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Nordingrå, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>670802</v>
+        <v>670795</v>
       </c>
       <c r="R89" t="n">
-        <v>6983219</v>
+        <v>6983095</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10565,7 +10563,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10575,7 +10573,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>I kalkgranskog, på mark med sparsamt fältskikt. Blåsippa, Vårärt, Skogsvicker, Vispstarr och Svart trolldruva nära. Ingen tall i närheten.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10586,6 +10589,11 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10602,10 +10610,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119788496</v>
+        <v>119898495</v>
       </c>
       <c r="B90" t="n">
-        <v>101097</v>
+        <v>57336</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10614,41 +10622,51 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>670807</v>
+        <v>670817</v>
       </c>
       <c r="R90" t="n">
-        <v>6983126</v>
+        <v>6983220</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10672,22 +10690,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10698,11 +10716,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10719,10 +10732,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119842147</v>
+        <v>119898669</v>
       </c>
       <c r="B91" t="n">
-        <v>105019</v>
+        <v>100194</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10735,34 +10748,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>224098</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Middagsklinten, Nordingrå, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>670795</v>
+        <v>670818</v>
       </c>
       <c r="R91" t="n">
-        <v>6983095</v>
+        <v>6983189</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10789,27 +10802,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>I kalkgranskog, på mark med sparsamt fältskikt. Blåsippa, Vårärt, Skogsvicker, Vispstarr och Svart trolldruva nära. Ingen tall i närheten.</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10841,10 +10849,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119898495</v>
+        <v>119898506</v>
       </c>
       <c r="B92" t="n">
-        <v>57336</v>
+        <v>101097</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10853,51 +10861,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670817</v>
+        <v>670802</v>
       </c>
       <c r="R92" t="n">
-        <v>6983220</v>
+        <v>6983219</v>
       </c>
       <c r="S92" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10926,7 +10924,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10936,7 +10934,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10947,6 +10945,11 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10963,10 +10966,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119898669</v>
+        <v>119898663</v>
       </c>
       <c r="B93" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10979,21 +10982,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11080,10 +11083,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119898506</v>
+        <v>119898932</v>
       </c>
       <c r="B94" t="n">
-        <v>101097</v>
+        <v>94346</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11096,21 +11099,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221235</v>
+        <v>2813</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11120,10 +11123,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>670802</v>
+        <v>670806</v>
       </c>
       <c r="R94" t="n">
-        <v>6983219</v>
+        <v>6983157</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11155,7 +11158,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11165,7 +11168,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11176,11 +11179,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11197,10 +11195,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119898663</v>
+        <v>119898984</v>
       </c>
       <c r="B95" t="n">
-        <v>100103</v>
+        <v>94334</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11213,21 +11211,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11237,10 +11235,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>670818</v>
+        <v>670792</v>
       </c>
       <c r="R95" t="n">
-        <v>6983189</v>
+        <v>6983157</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11272,7 +11270,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11282,7 +11280,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11293,11 +11291,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11314,10 +11307,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119898932</v>
+        <v>119899526</v>
       </c>
       <c r="B96" t="n">
-        <v>94346</v>
+        <v>105017</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11330,34 +11323,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>670806</v>
+        <v>670765</v>
       </c>
       <c r="R96" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11389,7 +11382,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11399,7 +11392,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11426,10 +11419,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119898984</v>
+        <v>119898844</v>
       </c>
       <c r="B97" t="n">
-        <v>94334</v>
+        <v>100194</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11442,21 +11435,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11466,10 +11459,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>670792</v>
+        <v>670832</v>
       </c>
       <c r="R97" t="n">
-        <v>6983157</v>
+        <v>6983190</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11501,7 +11494,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11511,7 +11504,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11538,10 +11531,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119899526</v>
+        <v>119898741</v>
       </c>
       <c r="B98" t="n">
-        <v>105017</v>
+        <v>100103</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11554,34 +11547,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221725</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>670765</v>
+        <v>670804</v>
       </c>
       <c r="R98" t="n">
-        <v>6983124</v>
+        <v>6983188</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11613,7 +11606,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11623,7 +11616,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11650,10 +11643,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119898844</v>
+        <v>119898937</v>
       </c>
       <c r="B99" t="n">
-        <v>100194</v>
+        <v>94334</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11666,21 +11659,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11690,10 +11683,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>670832</v>
+        <v>670806</v>
       </c>
       <c r="R99" t="n">
-        <v>6983190</v>
+        <v>6983157</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11725,7 +11718,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11735,7 +11728,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11762,10 +11755,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119898741</v>
+        <v>119898656</v>
       </c>
       <c r="B100" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11778,21 +11771,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11802,10 +11795,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>670804</v>
+        <v>670818</v>
       </c>
       <c r="R100" t="n">
-        <v>6983188</v>
+        <v>6983189</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11837,7 +11830,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11847,7 +11840,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11858,6 +11851,11 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11874,10 +11872,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119898937</v>
+        <v>119899557</v>
       </c>
       <c r="B101" t="n">
-        <v>94334</v>
+        <v>91512</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11890,34 +11888,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>670806</v>
+        <v>670765</v>
       </c>
       <c r="R101" t="n">
-        <v>6983157</v>
+        <v>6983124</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11949,7 +11947,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11959,7 +11957,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11986,10 +11984,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119898656</v>
+        <v>119900032</v>
       </c>
       <c r="B102" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12002,34 +12000,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>670818</v>
+        <v>670742</v>
       </c>
       <c r="R102" t="n">
-        <v>6983189</v>
+        <v>6983030</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12061,7 +12059,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12071,7 +12069,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12082,11 +12080,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12103,10 +12096,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119899557</v>
+        <v>119898913</v>
       </c>
       <c r="B103" t="n">
-        <v>91512</v>
+        <v>57336</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12115,38 +12108,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>670765</v>
+        <v>670820</v>
       </c>
       <c r="R103" t="n">
-        <v>6983124</v>
+        <v>6983158</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12178,7 +12171,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12188,7 +12181,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12215,10 +12208,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119899251</v>
+        <v>119898758</v>
       </c>
       <c r="B104" t="n">
-        <v>100103</v>
+        <v>91879</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12231,39 +12224,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>670777</v>
+        <v>670804</v>
       </c>
       <c r="R104" t="n">
-        <v>6983156</v>
+        <v>6983188</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12295,7 +12283,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12305,7 +12293,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12337,7 +12325,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119900032</v>
+        <v>119895594</v>
       </c>
       <c r="B105" t="n">
         <v>100103</v>
@@ -12373,14 +12361,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Nordingrå, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>670742</v>
+        <v>670802</v>
       </c>
       <c r="R105" t="n">
-        <v>6983030</v>
+        <v>6983219</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12412,7 +12400,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12422,7 +12410,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12449,10 +12437,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119899641</v>
+        <v>119895581</v>
       </c>
       <c r="B106" t="n">
-        <v>101097</v>
+        <v>91879</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12465,21 +12453,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12489,10 +12477,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>670779</v>
+        <v>670765</v>
       </c>
       <c r="R106" t="n">
-        <v>6983125</v>
+        <v>6983124</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12524,7 +12512,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12534,7 +12522,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12561,10 +12549,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119898913</v>
+        <v>120235119</v>
       </c>
       <c r="B107" t="n">
-        <v>57336</v>
+        <v>91562</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12573,41 +12561,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>670820</v>
+        <v>670847</v>
       </c>
       <c r="R107" t="n">
-        <v>6983158</v>
+        <v>6983132</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12631,22 +12619,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12661,22 +12639,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119898758</v>
+        <v>120235198</v>
       </c>
       <c r="B108" t="n">
-        <v>91879</v>
+        <v>100263</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12689,37 +12667,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>670804</v>
+        <v>670732</v>
       </c>
       <c r="R108" t="n">
-        <v>6983188</v>
+        <v>6983014</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12743,22 +12721,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12769,31 +12737,26 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119895594</v>
+        <v>120235197</v>
       </c>
       <c r="B109" t="n">
-        <v>100103</v>
+        <v>100263</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12806,37 +12769,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
+          <t>Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>670802</v>
+        <v>670768</v>
       </c>
       <c r="R109" t="n">
-        <v>6983219</v>
+        <v>6983085</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12860,22 +12823,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12890,22 +12843,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119895581</v>
+        <v>120235194</v>
       </c>
       <c r="B110" t="n">
-        <v>91879</v>
+        <v>100263</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12918,37 +12871,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Middagsklinten, Middagsklinten, Ång</t>
+          <t>Middagsklinten, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>670765</v>
+        <v>670904</v>
       </c>
       <c r="R110" t="n">
-        <v>6983124</v>
+        <v>6983156</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12972,22 +12925,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13002,22 +12945,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120235119</v>
+        <v>120235195</v>
       </c>
       <c r="B111" t="n">
-        <v>91562</v>
+        <v>100263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13030,21 +12973,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13054,10 +12997,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>670847</v>
+        <v>670813</v>
       </c>
       <c r="R111" t="n">
-        <v>6983132</v>
+        <v>6983126</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13116,10 +13059,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120235198</v>
+        <v>120235121</v>
       </c>
       <c r="B112" t="n">
-        <v>100263</v>
+        <v>100172</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13132,21 +13075,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13156,10 +13099,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>670732</v>
+        <v>670816</v>
       </c>
       <c r="R112" t="n">
-        <v>6983014</v>
+        <v>6983123</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13218,10 +13161,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120235197</v>
+        <v>120235122</v>
       </c>
       <c r="B113" t="n">
-        <v>100263</v>
+        <v>100172</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13234,21 +13177,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13320,10 +13263,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120235194</v>
+        <v>120235118</v>
       </c>
       <c r="B114" t="n">
-        <v>100263</v>
+        <v>91562</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13336,21 +13279,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13360,10 +13303,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>670904</v>
+        <v>670878</v>
       </c>
       <c r="R114" t="n">
-        <v>6983156</v>
+        <v>6983125</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13422,7 +13365,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120235195</v>
+        <v>120235196</v>
       </c>
       <c r="B115" t="n">
         <v>100263</v>
@@ -13462,10 +13405,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>670813</v>
+        <v>670779</v>
       </c>
       <c r="R115" t="n">
-        <v>6983126</v>
+        <v>6983095</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13524,10 +13467,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120235121</v>
+        <v>120235111</v>
       </c>
       <c r="B116" t="n">
-        <v>100172</v>
+        <v>101166</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13540,21 +13483,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13564,10 +13507,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>670816</v>
+        <v>670748</v>
       </c>
       <c r="R116" t="n">
-        <v>6983123</v>
+        <v>6982992</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13626,10 +13569,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120235122</v>
+        <v>121087115</v>
       </c>
       <c r="B117" t="n">
-        <v>100172</v>
+        <v>83080</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13638,41 +13581,36 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
+        <v>6003253</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Otidea mirabilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Bolognini &amp; Jamoni</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Middagsklinten, Ång</t>
+          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>670768</v>
+        <v>670790</v>
       </c>
       <c r="R117" t="n">
-        <v>6983085</v>
+        <v>6983188</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13696,12 +13634,27 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med mycket rikt fältskikt, både låg- och högörter (blåsippa, svart trolldruva, vårärt, skogsvicker, vispstarr, ormbär, torta). Ensam fruktkropp. Endast gran på växtplatsen men enstaka tallar i stråket.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13712,442 +13665,24 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Erik Persson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>120235118</v>
-      </c>
-      <c r="B118" t="n">
-        <v>91562</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>4769</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Svavelriska</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Middagsklinten, Ång</t>
-        </is>
-      </c>
-      <c r="Q118" t="n">
-        <v>670878</v>
-      </c>
-      <c r="R118" t="n">
-        <v>6983125</v>
-      </c>
-      <c r="S118" t="n">
-        <v>10</v>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>Nordingrå</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AD118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT118" t="inlineStr"/>
-      <c r="AW118" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>120235196</v>
-      </c>
-      <c r="B119" t="n">
-        <v>100263</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Middagsklinten, Ång</t>
-        </is>
-      </c>
-      <c r="Q119" t="n">
-        <v>670779</v>
-      </c>
-      <c r="R119" t="n">
-        <v>6983095</v>
-      </c>
-      <c r="S119" t="n">
-        <v>10</v>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>Nordingrå</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AD119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT119" t="inlineStr"/>
-      <c r="AW119" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>120235111</v>
-      </c>
-      <c r="B120" t="n">
-        <v>101166</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>221235</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Vårärt</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Lathyrus vernus</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Middagsklinten, Ång</t>
-        </is>
-      </c>
-      <c r="Q120" t="n">
-        <v>670748</v>
-      </c>
-      <c r="R120" t="n">
-        <v>6982992</v>
-      </c>
-      <c r="S120" t="n">
-        <v>10</v>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>Nordingrå</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AD120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT120" t="inlineStr"/>
-      <c r="AW120" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>121087115</v>
-      </c>
-      <c r="B121" t="n">
-        <v>83080</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>DD</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>6003253</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Otidea mirabilis</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Bolognini &amp; Jamoni</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Middagsklinten N, Nordingrå, Middagsklinten N, Nordingrå, Ång</t>
-        </is>
-      </c>
-      <c r="Q121" t="n">
-        <v>670790</v>
-      </c>
-      <c r="R121" t="n">
-        <v>6983188</v>
-      </c>
-      <c r="S121" t="n">
-        <v>25</v>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>Nordingrå</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>2024-09-15</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>2024-09-15</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med mycket rikt fältskikt, både låg- och högörter (blåsippa, svart trolldruva, vårärt, skogsvicker, vispstarr, ormbär, torta). Ensam fruktkropp. Endast gran på växtplatsen men enstaka tallar i stråket.</t>
-        </is>
-      </c>
-      <c r="AD121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT121" t="inlineStr"/>
-      <c r="AW121" t="inlineStr">
-        <is>
-          <t>Erik Persson</t>
-        </is>
-      </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>Erik Persson, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13684,6 +13684,113 @@
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126594697</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98397</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Middagsklinten, Ång</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>670731</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6982967</v>
+      </c>
+      <c r="S118" t="n">
+        <v>25</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -13689,7 +13689,7 @@
         <v>126594697</v>
       </c>
       <c r="B118" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -13689,7 +13689,7 @@
         <v>126594697</v>
       </c>
       <c r="B118" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -13689,7 +13689,7 @@
         <v>126594697</v>
       </c>
       <c r="B118" t="n">
-        <v>98478</v>
+        <v>98472</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -8212,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="AE68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
@@ -13689,7 +13689,7 @@
         <v>126594697</v>
       </c>
       <c r="B118" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 38014-2024 artfynd.xlsx
+++ b/artfynd/A 38014-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112361059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781414</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781418</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781392</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112362904</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781410</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789925</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119804612</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898937</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898984</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119900076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898932</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111838324</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111838270</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781465</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112362911</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507267</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363073</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112362927</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363008</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3033,6 +3143,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112362960</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781446</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3227,6 +3347,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781447</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3324,6 +3449,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781448</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3421,6 +3551,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781449</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3538,6 +3673,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788402</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112367070</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3743,6 +3888,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781368</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3840,6 +3990,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781369</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3937,6 +4092,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781370</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4049,6 +4209,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788716</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788926</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4268,6 +4438,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789399</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4375,6 +4550,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119804434</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4482,6 +4662,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119899557</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4579,6 +4764,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235118</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4676,6 +4866,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235119</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4793,6 +4988,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129302676</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4919,6 +5119,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112362953</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5045,6 +5250,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363071</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5142,6 +5352,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781438</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5239,6 +5454,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781439</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5336,6 +5556,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781440</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5443,6 +5668,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895581</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5555,6 +5785,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898758</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5652,6 +5887,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781385</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5775,6 +6015,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112856082</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5872,6 +6117,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781377</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5989,6 +6239,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788516</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6106,6 +6361,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898495</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6213,6 +6473,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898913</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6345,6 +6610,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103367612</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6453,6 +6723,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631280</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6584,6 +6859,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119341970</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6707,6 +6987,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95228109</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6825,6 +7110,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102467836</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6943,6 +7233,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102467870</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7061,6 +7356,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102467966</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7175,6 +7475,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377355</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7289,6 +7594,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377420</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7403,6 +7713,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377431</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7517,6 +7832,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377458</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7626,6 +7946,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377591</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7738,6 +8063,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111381644</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7846,6 +8176,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111381654</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7954,6 +8289,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111381657</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8062,6 +8402,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111381659</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8175,6 +8520,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631325</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8283,6 +8633,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631569</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8396,6 +8751,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631775</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8509,6 +8869,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631801</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8622,6 +8987,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113778170</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8734,6 +9104,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117494692</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8846,6 +9221,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117496085</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8958,6 +9338,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117521203</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9070,6 +9455,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117521233</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9182,6 +9572,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522413</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9294,6 +9689,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522437</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9391,6 +9791,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781348</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9488,6 +9893,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781350</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9585,6 +9995,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781352</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9682,6 +10097,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781353</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9794,6 +10214,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788496</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9906,6 +10331,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788561</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10018,6 +10448,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898506</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10130,6 +10565,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898656</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10237,6 +10677,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119899214</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10344,6 +10789,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119899767</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10441,6 +10891,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235111</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10548,6 +11003,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119899526</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10666,6 +11126,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97669944</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10784,6 +11249,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97669948</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10902,6 +11372,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97670064</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11020,6 +11495,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97670072</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11138,6 +11618,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102467878</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11256,6 +11741,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102467940</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11370,6 +11860,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377343</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11484,6 +11979,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377417</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11598,6 +12098,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377444</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11712,6 +12217,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377467</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11826,6 +12336,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377480</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11940,6 +12455,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377502</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12054,6 +12574,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377646</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12168,6 +12693,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377667</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12282,6 +12812,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103377703</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12399,6 +12934,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109628596</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12507,6 +13047,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111393025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12615,6 +13160,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111393147</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12728,6 +13278,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111393378</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12841,6 +13396,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631216</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12954,6 +13514,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631318</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13067,6 +13632,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631406</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13175,6 +13745,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631650</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13283,6 +13858,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631758</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13391,6 +13971,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631896</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13504,6 +14089,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112362935</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13611,6 +14201,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117494842</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13723,6 +14318,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117494953</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13830,6 +14430,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495052</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13937,6 +14542,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495258</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14049,6 +14659,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495636</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14156,6 +14771,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495789</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14263,6 +14883,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495994</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14370,6 +14995,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117521257</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14482,6 +15112,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522070</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14589,6 +15224,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522356</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14686,6 +15326,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781469</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14783,6 +15428,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781470</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14890,6 +15540,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788502</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14997,6 +15652,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788761</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15104,6 +15764,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788844</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15211,6 +15876,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788866</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15323,6 +15993,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788891</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15430,6 +16105,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788949</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15542,6 +16222,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789062</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15654,6 +16339,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789352</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15761,6 +16451,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789418</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15868,6 +16563,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789443</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15975,6 +16675,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789861</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16082,6 +16787,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119804575</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16189,6 +16899,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119804619</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16296,6 +17011,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895522</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16403,6 +17123,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898558</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16510,6 +17235,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898844</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16607,6 +17337,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235194</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16704,6 +17439,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235195</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16801,6 +17541,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235196</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16898,6 +17643,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235197</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16995,6 +17745,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235198</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17112,6 +17867,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110573188</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17220,6 +17980,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111381704</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17333,6 +18098,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631351</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17441,6 +18211,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631469</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17554,6 +18329,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631645</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17662,6 +18442,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112918582</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17779,6 +18564,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495741</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17896,6 +18686,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522160</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18003,6 +18798,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522210</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18115,6 +18915,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522336</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18222,6 +19027,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117522393</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18319,6 +19129,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781359</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18416,6 +19231,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781373</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18523,6 +19343,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789381</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18630,6 +19455,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789841</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18742,6 +19572,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119804571</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18849,6 +19684,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895587</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18956,6 +19796,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895594</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19063,6 +19908,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895635</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19175,6 +20025,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898663</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19282,6 +20137,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119898741</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19389,6 +20249,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119899751</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19496,6 +20361,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119900032</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19593,6 +20463,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235121</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19690,6 +20565,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120235122</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19811,6 +20691,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126571688</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19918,6 +20803,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126594697</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20016,6 +20906,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119781361</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20133,6 +21028,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119842147</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20250,8 +21150,195 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121087115</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>